--- a/door_switch_maze/grid/DQN_HER_mission/episode_rewards_her.xlsx
+++ b/door_switch_maze/grid/DQN_HER_mission/episode_rewards_her.xlsx
@@ -597,7 +597,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.3953125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -661,7 +661,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.89171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -693,7 +693,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.3039062499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -773,7 +773,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.35734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -805,7 +805,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.7075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -813,7 +813,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>0.6203125</v>
       </c>
     </row>
     <row r="49">
@@ -821,7 +821,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.76796875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -877,7 +877,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>0.7932812499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -925,7 +925,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>0.4796874999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -965,7 +965,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>0.7173437499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -973,7 +973,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>0.319375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -989,7 +989,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>0.84390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1005,7 +1005,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>0.87625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1045,7 +1045,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>0.3728125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1069,7 +1069,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>0.7946875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1085,7 +1085,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1093,7 +1093,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>0.69203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1101,7 +1101,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>0.87484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1109,7 +1109,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>0.8987499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1125,7 +1125,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>0.521875</v>
+        <v>0.3742187499999999</v>
       </c>
     </row>
     <row r="88">
@@ -1133,7 +1133,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>0.4445312499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -1149,7 +1149,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>0.6751562499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -1165,7 +1165,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>0.61609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1173,7 +1173,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>0.80171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1181,7 +1181,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>0.2982812500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -1189,7 +1189,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>0.6484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1197,7 +1197,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>0.775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -1213,7 +1213,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>0.6934374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -1221,7 +1221,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>0.68921875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -1237,7 +1237,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>0.81015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -1253,7 +1253,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>0.67234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -1261,7 +1261,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>0.6090625000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -1269,7 +1269,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>0.86640625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -1277,7 +1277,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>0.5753125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -1285,7 +1285,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>0.40234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -1293,7 +1293,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>0.6090625000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -1301,7 +1301,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>0.81015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -1309,7 +1309,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>0.63296875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -1317,7 +1317,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>0.454375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -1325,7 +1325,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>0.63015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -1349,7 +1349,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>0.5823437499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -1365,7 +1365,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>0.9240625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -1373,7 +1373,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>0.63296875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -1397,7 +1397,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>0.6709375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -1405,7 +1405,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>0.5134375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -1413,7 +1413,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>0.84671875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -1421,7 +1421,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>0.5795312500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -1437,7 +1437,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>0.6174999999999999</v>
       </c>
     </row>
     <row r="127">
@@ -1445,7 +1445,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>0.78203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -1469,7 +1469,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>0.59078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -1509,7 +1509,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>0.296875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -1525,7 +1525,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>0.499375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -1541,7 +1541,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>0.39390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -1549,7 +1549,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>0.60625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -1557,7 +1557,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>0.7229687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -1581,7 +1581,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>0.61046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -1597,7 +1597,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>0.58375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -1613,7 +1613,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>0.67234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -1621,7 +1621,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -1629,7 +1629,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>0.80171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -1645,7 +1645,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>0.54859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -1653,7 +1653,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>0.5992187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -1677,7 +1677,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>0.70328125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -1709,7 +1709,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>0</v>
+        <v>0.47546875</v>
       </c>
     </row>
     <row r="161">
@@ -1717,7 +1717,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>0.5035937500000001</v>
+        <v>0.3643749999999999</v>
       </c>
     </row>
     <row r="162">
@@ -1741,7 +1741,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>0.42484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -1773,7 +1773,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>0.5401562499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -1781,7 +1781,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>0.80171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -1789,7 +1789,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>0.5640624999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -1813,7 +1813,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>0.82984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -1821,7 +1821,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>0.7103124999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -1845,7 +1845,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>0.49515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -1861,7 +1861,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>0</v>
+        <v>0.42625</v>
       </c>
     </row>
     <row r="180">
@@ -1877,7 +1877,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>0.35453125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -1885,7 +1885,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>0.3896875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -1917,7 +1917,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>0.44875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -1925,7 +1925,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>0.68078125</v>
+        <v>0.6315625</v>
       </c>
     </row>
     <row r="188">
@@ -1949,7 +1949,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>0.6090625000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -2005,7 +2005,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>0.8003125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -2013,7 +2013,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>0.6315625</v>
       </c>
     </row>
     <row r="199">
@@ -2037,7 +2037,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>0.7201562500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -2045,7 +2045,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="n">
-        <v>0.86640625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -2053,7 +2053,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>0.8256250000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -2061,7 +2061,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>0.46703125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -2101,7 +2101,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>0.4332812500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -2109,7 +2109,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="n">
-        <v>0</v>
+        <v>0.84109375</v>
       </c>
     </row>
     <row r="211">
@@ -2125,7 +2125,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="n">
-        <v>0.319375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -2133,7 +2133,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="n">
-        <v>0.77078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -2141,7 +2141,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="n">
-        <v>0.578125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -2149,7 +2149,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="n">
-        <v>0.8453125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -2165,7 +2165,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>0</v>
+        <v>0.63015625</v>
       </c>
     </row>
     <row r="218">
@@ -2181,7 +2181,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="n">
-        <v>0.4375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -2197,7 +2197,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="n">
-        <v>0.3109375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -2205,7 +2205,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>0.8565625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -2221,7 +2221,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="n">
-        <v>0.6737500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -2237,7 +2237,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="n">
-        <v>0.61328125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -2253,7 +2253,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>0.775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -2285,7 +2285,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="n">
-        <v>0.49234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -2293,7 +2293,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="n">
-        <v>0.74125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -2309,7 +2309,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>0.3657812499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -2317,7 +2317,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>0.45296875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -2333,7 +2333,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="n">
-        <v>0.39671875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -2341,7 +2341,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>0.74125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -2357,7 +2357,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="n">
-        <v>0.6850000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -2365,7 +2365,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="n">
-        <v>0.5879687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -2381,7 +2381,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="n">
-        <v>0.78203125</v>
+        <v>0.35875</v>
       </c>
     </row>
     <row r="245">
@@ -2405,7 +2405,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="n">
-        <v>0</v>
+        <v>0.8607812500000001</v>
       </c>
     </row>
     <row r="248">
@@ -2413,7 +2413,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>0.4965625</v>
       </c>
     </row>
     <row r="249">
@@ -2453,7 +2453,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="n">
-        <v>0.49796875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -2461,7 +2461,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>0.4009374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -2493,7 +2493,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="n">
-        <v>0.4009374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -2509,7 +2509,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="n">
-        <v>0.386875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -2517,7 +2517,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="n">
-        <v>0.7834375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -2541,7 +2541,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="n">
-        <v>0.70046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -2549,7 +2549,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="n">
-        <v>0</v>
+        <v>0.46703125</v>
       </c>
     </row>
     <row r="266">
@@ -2557,7 +2557,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>0.8635937499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -2589,7 +2589,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -2613,7 +2613,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="n">
-        <v>0.56125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -2653,7 +2653,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="n">
-        <v>0.8987499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -2685,7 +2685,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="n">
-        <v>0.3840625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -2693,7 +2693,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="n">
-        <v>0.6737500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -2733,7 +2733,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="n">
-        <v>0.8495312500000001</v>
+        <v>0.87484375</v>
       </c>
     </row>
     <row r="289">
@@ -2749,7 +2749,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="n">
-        <v>0.3165625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -2765,7 +2765,7 @@
         <v>291</v>
       </c>
       <c r="B292" t="n">
-        <v>0.80453125</v>
+        <v>0.5064062499999999</v>
       </c>
     </row>
     <row r="293">
@@ -2781,7 +2781,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="n">
-        <v>0.62875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -2797,7 +2797,7 @@
         <v>295</v>
       </c>
       <c r="B296" t="n">
-        <v>0.465625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -2813,7 +2813,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>0.5049999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -2829,7 +2829,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="n">
-        <v>0.8565625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -2837,7 +2837,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="n">
-        <v>0.93671875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -2845,7 +2845,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="n">
-        <v>0.91140625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -2861,7 +2861,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="n">
-        <v>0.71171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -2909,7 +2909,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="n">
-        <v>0.81859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -2933,7 +2933,7 @@
         <v>312</v>
       </c>
       <c r="B313" t="n">
-        <v>0.8453125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -2941,7 +2941,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="n">
-        <v>0.3475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -2949,7 +2949,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>0.82703125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -2957,7 +2957,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="n">
-        <v>0.9296875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -2965,7 +2965,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="n">
-        <v>0.7440625000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -2973,7 +2973,7 @@
         <v>317</v>
       </c>
       <c r="B318" t="n">
-        <v>0.83265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -2989,7 +2989,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>0.7173437499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -2997,7 +2997,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="n">
-        <v>0.90296875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -3005,7 +3005,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="n">
-        <v>0.926875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -3021,7 +3021,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="n">
-        <v>0</v>
+        <v>0.34328125</v>
       </c>
     </row>
     <row r="325">
@@ -3029,7 +3029,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="n">
-        <v>0.3854687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -3069,7 +3069,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="n">
-        <v>0.8959375000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -3093,7 +3093,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="n">
-        <v>0.49796875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -3125,7 +3125,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="n">
-        <v>0.9310937500000001</v>
+        <v>0.6498437500000001</v>
       </c>
     </row>
     <row r="338">
@@ -3133,7 +3133,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="n">
-        <v>0.63296875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -3165,7 +3165,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="n">
-        <v>0.955</v>
+        <v>0.5753125</v>
       </c>
     </row>
     <row r="343">
@@ -3205,7 +3205,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="n">
-        <v>0.81578125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
@@ -3213,7 +3213,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="n">
-        <v>0.87484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -3245,7 +3245,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="n">
-        <v>0.8579687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -3253,7 +3253,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="n">
-        <v>0.6174999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -3269,7 +3269,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="n">
-        <v>0.96203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356">
@@ -3277,7 +3277,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="n">
-        <v>0.865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -3293,7 +3293,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="n">
-        <v>0.955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -3317,7 +3317,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="n">
-        <v>0.94375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
@@ -3325,7 +3325,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="n">
-        <v>0.7946875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363">
@@ -3373,7 +3373,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="n">
-        <v>0.949375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369">
@@ -3381,7 +3381,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="n">
-        <v>0.9690625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370">
@@ -3389,7 +3389,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="n">
-        <v>0.5092187500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -3397,7 +3397,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="n">
-        <v>0.96765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372">
@@ -3405,7 +3405,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="n">
-        <v>0.92265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -3413,7 +3413,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="n">
-        <v>0.8143750000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -3429,7 +3429,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="n">
-        <v>0.6596875</v>
+        <v>0.645625</v>
       </c>
     </row>
     <row r="376">
@@ -3437,7 +3437,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="n">
-        <v>0.8171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -3445,7 +3445,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="n">
-        <v>0.7103124999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378">
@@ -3461,7 +3461,7 @@
         <v>378</v>
       </c>
       <c r="B379" t="n">
-        <v>0.5696874999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -3485,7 +3485,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="n">
-        <v>0.7440625000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -3493,7 +3493,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="n">
-        <v>0.4684375000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -3517,7 +3517,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="n">
-        <v>0.971875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -3533,7 +3533,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="n">
-        <v>0</v>
+        <v>0.47546875</v>
       </c>
     </row>
     <row r="389">
@@ -3541,7 +3541,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="n">
-        <v>0.89171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -3549,7 +3549,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="n">
-        <v>0.9803125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
@@ -3557,7 +3557,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="n">
-        <v>0.94796875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
@@ -3573,7 +3573,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="n">
-        <v>0.95359375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="394">
@@ -3581,7 +3581,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="n">
-        <v>0.8846875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -3589,7 +3589,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="n">
-        <v>0.84390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396">
@@ -3597,7 +3597,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="n">
-        <v>0.77078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -3605,7 +3605,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="n">
-        <v>0.95921875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -3621,7 +3621,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="n">
-        <v>0.836875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
@@ -3629,7 +3629,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="n">
-        <v>0.81859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401">
@@ -3661,7 +3661,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="n">
-        <v>0.8143750000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405">
@@ -3685,7 +3685,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="n">
-        <v>0.95078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -3701,7 +3701,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="n">
-        <v>0.859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410">
@@ -3717,7 +3717,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="n">
-        <v>0.6442187500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412">
@@ -3733,7 +3733,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="n">
-        <v>0.5725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414">
@@ -3741,7 +3741,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="n">
-        <v>0.9310937500000001</v>
+        <v>0.74125</v>
       </c>
     </row>
     <row r="415">
@@ -3749,7 +3749,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="n">
-        <v>0.82984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416">
@@ -3757,7 +3757,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="n">
-        <v>0.9662500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417">
@@ -3781,7 +3781,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="n">
-        <v>0.3039062499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -3805,7 +3805,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="n">
-        <v>0.865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423">
@@ -3813,7 +3813,7 @@
         <v>422</v>
       </c>
       <c r="B423" t="n">
-        <v>0.60765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424">
@@ -3829,7 +3829,7 @@
         <v>424</v>
       </c>
       <c r="B425" t="n">
-        <v>0.904375</v>
+        <v>0.5795312500000001</v>
       </c>
     </row>
     <row r="426">
@@ -3845,7 +3845,7 @@
         <v>426</v>
       </c>
       <c r="B427" t="n">
-        <v>0.8734375</v>
+        <v>0.7159375</v>
       </c>
     </row>
     <row r="428">
@@ -3861,7 +3861,7 @@
         <v>428</v>
       </c>
       <c r="B429" t="n">
-        <v>0.645625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="430">
@@ -3869,7 +3869,7 @@
         <v>429</v>
       </c>
       <c r="B430" t="n">
-        <v>0</v>
+        <v>0.46140625</v>
       </c>
     </row>
     <row r="431">
@@ -3877,7 +3877,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="n">
-        <v>0.7792187500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="432">
@@ -3901,7 +3901,7 @@
         <v>433</v>
       </c>
       <c r="B434" t="n">
-        <v>0.6596875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="435">
@@ -3909,7 +3909,7 @@
         <v>434</v>
       </c>
       <c r="B435" t="n">
-        <v>0.6765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436">
@@ -3925,7 +3925,7 @@
         <v>436</v>
       </c>
       <c r="B437" t="n">
-        <v>0.713125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -3933,7 +3933,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="n">
-        <v>0</v>
+        <v>0.49796875</v>
       </c>
     </row>
     <row r="439">
@@ -3941,7 +3941,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="n">
-        <v>0.3039062499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440">
@@ -3949,7 +3949,7 @@
         <v>439</v>
       </c>
       <c r="B440" t="n">
-        <v>0.6850000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441">
@@ -3957,7 +3957,7 @@
         <v>440</v>
       </c>
       <c r="B441" t="n">
-        <v>0.84390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="442">
@@ -3965,7 +3965,7 @@
         <v>441</v>
       </c>
       <c r="B442" t="n">
-        <v>0</v>
+        <v>0.8734375</v>
       </c>
     </row>
     <row r="443">
@@ -3973,7 +3973,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="n">
-        <v>0</v>
+        <v>0.94234375</v>
       </c>
     </row>
     <row r="444">
@@ -3981,7 +3981,7 @@
         <v>443</v>
       </c>
       <c r="B444" t="n">
-        <v>0.62171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445">
@@ -3989,7 +3989,7 @@
         <v>444</v>
       </c>
       <c r="B445" t="n">
-        <v>0.41078125</v>
+        <v>0.4965625</v>
       </c>
     </row>
     <row r="446">
@@ -3997,7 +3997,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="n">
-        <v>0.960625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447">
@@ -4005,7 +4005,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="n">
-        <v>0.865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448">
@@ -4029,7 +4029,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="n">
-        <v>0.7159375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451">
@@ -4037,7 +4037,7 @@
         <v>450</v>
       </c>
       <c r="B451" t="n">
-        <v>0.6470312499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452">
@@ -4053,7 +4053,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="n">
-        <v>0.8059375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -4069,7 +4069,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="n">
-        <v>0</v>
+        <v>0.7890625</v>
       </c>
     </row>
     <row r="456">
@@ -4093,7 +4093,7 @@
         <v>457</v>
       </c>
       <c r="B458" t="n">
-        <v>0.87765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="459">
@@ -4157,7 +4157,7 @@
         <v>465</v>
       </c>
       <c r="B466" t="n">
-        <v>0.915625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467">
@@ -4165,7 +4165,7 @@
         <v>466</v>
       </c>
       <c r="B467" t="n">
-        <v>0</v>
+        <v>0.6498437500000001</v>
       </c>
     </row>
     <row r="468">
@@ -4189,7 +4189,7 @@
         <v>469</v>
       </c>
       <c r="B470" t="n">
-        <v>0.85234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471">
@@ -4205,7 +4205,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="n">
-        <v>0.61328125</v>
+        <v>0.5275</v>
       </c>
     </row>
     <row r="473">
@@ -4213,7 +4213,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="n">
-        <v>0.5443750000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474">
@@ -4245,7 +4245,7 @@
         <v>476</v>
       </c>
       <c r="B477" t="n">
-        <v>0</v>
+        <v>0.431875</v>
       </c>
     </row>
     <row r="478">
@@ -4261,7 +4261,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="n">
-        <v>0</v>
+        <v>0.3925</v>
       </c>
     </row>
     <row r="480">
@@ -4269,7 +4269,7 @@
         <v>479</v>
       </c>
       <c r="B480" t="n">
-        <v>0.77359375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="481">
@@ -4277,7 +4277,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="n">
-        <v>0.6315625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="482">
@@ -4285,7 +4285,7 @@
         <v>481</v>
       </c>
       <c r="B482" t="n">
-        <v>0.7496875000000001</v>
+        <v>0.69765625</v>
       </c>
     </row>
     <row r="483">
@@ -4301,7 +4301,7 @@
         <v>483</v>
       </c>
       <c r="B484" t="n">
-        <v>0</v>
+        <v>0.645625</v>
       </c>
     </row>
     <row r="485">
@@ -4317,7 +4317,7 @@
         <v>485</v>
       </c>
       <c r="B486" t="n">
-        <v>0</v>
+        <v>0.62171875</v>
       </c>
     </row>
     <row r="487">
@@ -4349,7 +4349,7 @@
         <v>489</v>
       </c>
       <c r="B490" t="n">
-        <v>0.77640625</v>
+        <v>0.791875</v>
       </c>
     </row>
     <row r="491">
@@ -4357,7 +4357,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="n">
-        <v>0</v>
+        <v>0.465625</v>
       </c>
     </row>
     <row r="492">
@@ -4373,7 +4373,7 @@
         <v>492</v>
       </c>
       <c r="B493" t="n">
-        <v>0</v>
+        <v>0.960625</v>
       </c>
     </row>
     <row r="494">
@@ -4381,7 +4381,7 @@
         <v>493</v>
       </c>
       <c r="B494" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.56546875</v>
       </c>
     </row>
     <row r="495">
@@ -4397,7 +4397,7 @@
         <v>495</v>
       </c>
       <c r="B496" t="n">
-        <v>0.82421875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="497">
@@ -4413,7 +4413,7 @@
         <v>497</v>
       </c>
       <c r="B498" t="n">
-        <v>0</v>
+        <v>0.83546875</v>
       </c>
     </row>
     <row r="499">
@@ -4429,7 +4429,7 @@
         <v>499</v>
       </c>
       <c r="B500" t="n">
-        <v>0.71875</v>
+        <v>0.94234375</v>
       </c>
     </row>
     <row r="501">
@@ -4437,7 +4437,7 @@
         <v>500</v>
       </c>
       <c r="B501" t="n">
-        <v>0.8621875</v>
+        <v>0.3840625</v>
       </c>
     </row>
     <row r="502">
@@ -4445,7 +4445,7 @@
         <v>501</v>
       </c>
       <c r="B502" t="n">
-        <v>0</v>
+        <v>0.308125</v>
       </c>
     </row>
     <row r="503">
@@ -4461,7 +4461,7 @@
         <v>503</v>
       </c>
       <c r="B504" t="n">
-        <v>0</v>
+        <v>0.32078125</v>
       </c>
     </row>
     <row r="505">
@@ -4477,7 +4477,7 @@
         <v>505</v>
       </c>
       <c r="B506" t="n">
-        <v>0</v>
+        <v>0.7173437499999999</v>
       </c>
     </row>
     <row r="507">
@@ -4517,7 +4517,7 @@
         <v>510</v>
       </c>
       <c r="B511" t="n">
-        <v>0</v>
+        <v>0.51625</v>
       </c>
     </row>
     <row r="512">
@@ -4525,7 +4525,7 @@
         <v>511</v>
       </c>
       <c r="B512" t="n">
-        <v>0</v>
+        <v>0.6203125</v>
       </c>
     </row>
     <row r="513">
@@ -4533,7 +4533,7 @@
         <v>512</v>
       </c>
       <c r="B513" t="n">
-        <v>0.48953125</v>
+        <v>0.3010937499999999</v>
       </c>
     </row>
     <row r="514">
@@ -4541,7 +4541,7 @@
         <v>513</v>
       </c>
       <c r="B514" t="n">
-        <v>0</v>
+        <v>0.53734375</v>
       </c>
     </row>
     <row r="515">
@@ -4549,7 +4549,7 @@
         <v>514</v>
       </c>
       <c r="B515" t="n">
-        <v>0</v>
+        <v>0.88609375</v>
       </c>
     </row>
     <row r="516">
@@ -4557,7 +4557,7 @@
         <v>515</v>
       </c>
       <c r="B516" t="n">
-        <v>0</v>
+        <v>0.848125</v>
       </c>
     </row>
     <row r="517">
@@ -4565,7 +4565,7 @@
         <v>516</v>
       </c>
       <c r="B517" t="n">
-        <v>0</v>
+        <v>0.6484375</v>
       </c>
     </row>
     <row r="518">
@@ -4573,7 +4573,7 @@
         <v>517</v>
       </c>
       <c r="B518" t="n">
-        <v>0</v>
+        <v>0.86640625</v>
       </c>
     </row>
     <row r="519">
@@ -4581,7 +4581,7 @@
         <v>518</v>
       </c>
       <c r="B519" t="n">
-        <v>0</v>
+        <v>0.3221875</v>
       </c>
     </row>
     <row r="520">
@@ -4589,7 +4589,7 @@
         <v>519</v>
       </c>
       <c r="B520" t="n">
-        <v>0</v>
+        <v>0.62875</v>
       </c>
     </row>
     <row r="521">
@@ -4605,7 +4605,7 @@
         <v>521</v>
       </c>
       <c r="B522" t="n">
-        <v>0</v>
+        <v>0.91703125</v>
       </c>
     </row>
     <row r="523">
@@ -4613,7 +4613,7 @@
         <v>522</v>
       </c>
       <c r="B523" t="n">
-        <v>0</v>
+        <v>0.94515625</v>
       </c>
     </row>
     <row r="524">
@@ -4621,7 +4621,7 @@
         <v>523</v>
       </c>
       <c r="B524" t="n">
-        <v>0.2982812500000001</v>
+        <v>0.9325</v>
       </c>
     </row>
     <row r="525">
@@ -4653,7 +4653,7 @@
         <v>527</v>
       </c>
       <c r="B528" t="n">
-        <v>0</v>
+        <v>0.9409375</v>
       </c>
     </row>
     <row r="529">
@@ -4661,7 +4661,7 @@
         <v>528</v>
       </c>
       <c r="B529" t="n">
-        <v>0</v>
+        <v>0.6625</v>
       </c>
     </row>
     <row r="530">
@@ -4669,7 +4669,7 @@
         <v>529</v>
       </c>
       <c r="B530" t="n">
-        <v>0</v>
+        <v>0.5049999999999999</v>
       </c>
     </row>
     <row r="531">
@@ -4693,7 +4693,7 @@
         <v>532</v>
       </c>
       <c r="B533" t="n">
-        <v>0.5739062500000001</v>
+        <v>0.4121875</v>
       </c>
     </row>
     <row r="534">
@@ -4709,7 +4709,7 @@
         <v>534</v>
       </c>
       <c r="B535" t="n">
-        <v>0</v>
+        <v>0.915625</v>
       </c>
     </row>
     <row r="536">
@@ -4717,7 +4717,7 @@
         <v>535</v>
       </c>
       <c r="B536" t="n">
-        <v>0.7075</v>
+        <v>0.37703125</v>
       </c>
     </row>
     <row r="537">
@@ -4733,7 +4733,7 @@
         <v>537</v>
       </c>
       <c r="B538" t="n">
-        <v>0</v>
+        <v>0.7089062500000001</v>
       </c>
     </row>
     <row r="539">
@@ -4741,7 +4741,7 @@
         <v>538</v>
       </c>
       <c r="B539" t="n">
-        <v>0.3995312499999999</v>
+        <v>0.82984375</v>
       </c>
     </row>
     <row r="540">
@@ -4749,7 +4749,7 @@
         <v>539</v>
       </c>
       <c r="B540" t="n">
-        <v>0</v>
+        <v>0.81859375</v>
       </c>
     </row>
     <row r="541">
@@ -4757,7 +4757,7 @@
         <v>540</v>
       </c>
       <c r="B541" t="n">
-        <v>0</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="542">
@@ -4765,7 +4765,7 @@
         <v>541</v>
       </c>
       <c r="B542" t="n">
-        <v>0</v>
+        <v>0.488125</v>
       </c>
     </row>
     <row r="543">
@@ -4789,7 +4789,7 @@
         <v>544</v>
       </c>
       <c r="B545" t="n">
-        <v>0</v>
+        <v>0.82140625</v>
       </c>
     </row>
     <row r="546">
@@ -4813,7 +4813,7 @@
         <v>547</v>
       </c>
       <c r="B548" t="n">
-        <v>0</v>
+        <v>0.859375</v>
       </c>
     </row>
     <row r="549">
@@ -4821,7 +4821,7 @@
         <v>548</v>
       </c>
       <c r="B549" t="n">
-        <v>0.533125</v>
+        <v>0.77078125</v>
       </c>
     </row>
     <row r="550">
@@ -4829,7 +4829,7 @@
         <v>549</v>
       </c>
       <c r="B550" t="n">
-        <v>0</v>
+        <v>0.6765625</v>
       </c>
     </row>
     <row r="551">
@@ -4837,7 +4837,7 @@
         <v>550</v>
       </c>
       <c r="B551" t="n">
-        <v>0</v>
+        <v>0.55703125</v>
       </c>
     </row>
     <row r="552">
@@ -4845,7 +4845,7 @@
         <v>551</v>
       </c>
       <c r="B552" t="n">
-        <v>0</v>
+        <v>0.848125</v>
       </c>
     </row>
     <row r="553">
@@ -4853,7 +4853,7 @@
         <v>552</v>
       </c>
       <c r="B553" t="n">
-        <v>0</v>
+        <v>0.74265625</v>
       </c>
     </row>
     <row r="554">
@@ -4861,7 +4861,7 @@
         <v>553</v>
       </c>
       <c r="B554" t="n">
-        <v>0</v>
+        <v>0.88890625</v>
       </c>
     </row>
     <row r="555">
@@ -4869,7 +4869,7 @@
         <v>554</v>
       </c>
       <c r="B555" t="n">
-        <v>0</v>
+        <v>0.82421875</v>
       </c>
     </row>
     <row r="556">
@@ -4877,7 +4877,7 @@
         <v>555</v>
       </c>
       <c r="B556" t="n">
-        <v>0.595</v>
+        <v>0.81859375</v>
       </c>
     </row>
     <row r="557">
@@ -4893,7 +4893,7 @@
         <v>557</v>
       </c>
       <c r="B558" t="n">
-        <v>0</v>
+        <v>0.90859375</v>
       </c>
     </row>
     <row r="559">
@@ -4901,7 +4901,7 @@
         <v>558</v>
       </c>
       <c r="B559" t="n">
-        <v>0</v>
+        <v>0.83125</v>
       </c>
     </row>
     <row r="560">
@@ -4909,7 +4909,7 @@
         <v>559</v>
       </c>
       <c r="B560" t="n">
-        <v>0</v>
+        <v>0.87625</v>
       </c>
     </row>
     <row r="561">
@@ -4917,7 +4917,7 @@
         <v>560</v>
       </c>
       <c r="B561" t="n">
-        <v>0</v>
+        <v>0.3010937499999999</v>
       </c>
     </row>
     <row r="562">
@@ -4933,7 +4933,7 @@
         <v>562</v>
       </c>
       <c r="B563" t="n">
-        <v>0.35453125</v>
+        <v>0.65546875</v>
       </c>
     </row>
     <row r="564">
@@ -4941,7 +4941,7 @@
         <v>563</v>
       </c>
       <c r="B564" t="n">
-        <v>0</v>
+        <v>0.80453125</v>
       </c>
     </row>
     <row r="565">
@@ -4949,7 +4949,7 @@
         <v>564</v>
       </c>
       <c r="B565" t="n">
-        <v>0</v>
+        <v>0.8678125</v>
       </c>
     </row>
     <row r="566">
@@ -4973,7 +4973,7 @@
         <v>567</v>
       </c>
       <c r="B568" t="n">
-        <v>0</v>
+        <v>0.89171875</v>
       </c>
     </row>
     <row r="569">
@@ -4981,7 +4981,7 @@
         <v>568</v>
       </c>
       <c r="B569" t="n">
-        <v>0</v>
+        <v>0.9184375</v>
       </c>
     </row>
     <row r="570">
@@ -4989,7 +4989,7 @@
         <v>569</v>
       </c>
       <c r="B570" t="n">
-        <v>0</v>
+        <v>0.88046875</v>
       </c>
     </row>
     <row r="571">
@@ -4997,7 +4997,7 @@
         <v>570</v>
       </c>
       <c r="B571" t="n">
-        <v>0</v>
+        <v>0.90859375</v>
       </c>
     </row>
     <row r="572">
@@ -5005,7 +5005,7 @@
         <v>571</v>
       </c>
       <c r="B572" t="n">
-        <v>0.6751562499999999</v>
+        <v>0.9071875</v>
       </c>
     </row>
     <row r="573">
@@ -5013,7 +5013,7 @@
         <v>572</v>
       </c>
       <c r="B573" t="n">
-        <v>0</v>
+        <v>0.9409375</v>
       </c>
     </row>
     <row r="574">
@@ -5021,7 +5021,7 @@
         <v>573</v>
       </c>
       <c r="B574" t="n">
-        <v>0</v>
+        <v>0.74265625</v>
       </c>
     </row>
     <row r="575">
@@ -5029,7 +5029,7 @@
         <v>574</v>
       </c>
       <c r="B575" t="n">
-        <v>0</v>
+        <v>0.87625</v>
       </c>
     </row>
     <row r="576">
@@ -5045,7 +5045,7 @@
         <v>576</v>
       </c>
       <c r="B577" t="n">
-        <v>0</v>
+        <v>0.8931249999999999</v>
       </c>
     </row>
     <row r="578">
@@ -5061,7 +5061,7 @@
         <v>578</v>
       </c>
       <c r="B579" t="n">
-        <v>0</v>
+        <v>0.76796875</v>
       </c>
     </row>
     <row r="580">
@@ -5077,7 +5077,7 @@
         <v>580</v>
       </c>
       <c r="B581" t="n">
-        <v>0</v>
+        <v>0.4389062500000001</v>
       </c>
     </row>
     <row r="582">
@@ -5085,7 +5085,7 @@
         <v>581</v>
       </c>
       <c r="B582" t="n">
-        <v>0</v>
+        <v>0.6793750000000001</v>
       </c>
     </row>
     <row r="583">
@@ -5101,7 +5101,7 @@
         <v>583</v>
       </c>
       <c r="B584" t="n">
-        <v>0</v>
+        <v>0.68921875</v>
       </c>
     </row>
     <row r="585">
@@ -5109,7 +5109,7 @@
         <v>584</v>
       </c>
       <c r="B585" t="n">
-        <v>0</v>
+        <v>0.3714062499999999</v>
       </c>
     </row>
     <row r="586">
@@ -5117,7 +5117,7 @@
         <v>585</v>
       </c>
       <c r="B586" t="n">
-        <v>0</v>
+        <v>0.85375</v>
       </c>
     </row>
     <row r="587">
@@ -5133,7 +5133,7 @@
         <v>587</v>
       </c>
       <c r="B588" t="n">
-        <v>0</v>
+        <v>0.87484375</v>
       </c>
     </row>
     <row r="589">
@@ -5141,7 +5141,7 @@
         <v>588</v>
       </c>
       <c r="B589" t="n">
-        <v>0</v>
+        <v>0.308125</v>
       </c>
     </row>
     <row r="590">
@@ -5157,7 +5157,7 @@
         <v>590</v>
       </c>
       <c r="B591" t="n">
-        <v>0</v>
+        <v>0.48109375</v>
       </c>
     </row>
     <row r="592">
@@ -5165,7 +5165,7 @@
         <v>591</v>
       </c>
       <c r="B592" t="n">
-        <v>0.7946875</v>
+        <v>0.803125</v>
       </c>
     </row>
     <row r="593">
@@ -5181,7 +5181,7 @@
         <v>593</v>
       </c>
       <c r="B594" t="n">
-        <v>0</v>
+        <v>0.6231249999999999</v>
       </c>
     </row>
     <row r="595">
@@ -5197,7 +5197,7 @@
         <v>595</v>
       </c>
       <c r="B596" t="n">
-        <v>0</v>
+        <v>0.5275</v>
       </c>
     </row>
     <row r="597">
@@ -5205,7 +5205,7 @@
         <v>596</v>
       </c>
       <c r="B597" t="n">
-        <v>0</v>
+        <v>0.6484375</v>
       </c>
     </row>
     <row r="598">
@@ -5213,7 +5213,7 @@
         <v>597</v>
       </c>
       <c r="B598" t="n">
-        <v>0</v>
+        <v>0.75671875</v>
       </c>
     </row>
     <row r="599">
@@ -5229,7 +5229,7 @@
         <v>599</v>
       </c>
       <c r="B600" t="n">
-        <v>0.56546875</v>
+        <v>0.926875</v>
       </c>
     </row>
     <row r="601">
@@ -5237,7 +5237,7 @@
         <v>600</v>
       </c>
       <c r="B601" t="n">
-        <v>0.5992187499999999</v>
+        <v>0.90578125</v>
       </c>
     </row>
     <row r="602">
@@ -5245,7 +5245,7 @@
         <v>601</v>
       </c>
       <c r="B602" t="n">
-        <v>0.45859375</v>
+        <v>0.9282812499999999</v>
       </c>
     </row>
     <row r="603">
@@ -5253,7 +5253,7 @@
         <v>602</v>
       </c>
       <c r="B603" t="n">
-        <v>0.82703125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="604">
@@ -5261,7 +5261,7 @@
         <v>603</v>
       </c>
       <c r="B604" t="n">
-        <v>0.7089062500000001</v>
+        <v>0.9634374999999999</v>
       </c>
     </row>
     <row r="605">
@@ -5269,7 +5269,7 @@
         <v>604</v>
       </c>
       <c r="B605" t="n">
-        <v>0</v>
+        <v>0.8846875</v>
       </c>
     </row>
     <row r="606">
@@ -5277,7 +5277,7 @@
         <v>605</v>
       </c>
       <c r="B606" t="n">
-        <v>0</v>
+        <v>0.9240625</v>
       </c>
     </row>
     <row r="607">
@@ -5285,7 +5285,7 @@
         <v>606</v>
       </c>
       <c r="B607" t="n">
-        <v>0</v>
+        <v>0.95359375</v>
       </c>
     </row>
     <row r="608">
@@ -5293,7 +5293,7 @@
         <v>607</v>
       </c>
       <c r="B608" t="n">
-        <v>0.69203125</v>
+        <v>0.95640625</v>
       </c>
     </row>
     <row r="609">
@@ -5301,7 +5301,7 @@
         <v>608</v>
       </c>
       <c r="B609" t="n">
-        <v>0</v>
+        <v>0.713125</v>
       </c>
     </row>
     <row r="610">
@@ -5317,7 +5317,7 @@
         <v>610</v>
       </c>
       <c r="B611" t="n">
-        <v>0.85375</v>
+        <v>0.791875</v>
       </c>
     </row>
     <row r="612">
@@ -5325,7 +5325,7 @@
         <v>611</v>
       </c>
       <c r="B612" t="n">
-        <v>0.74125</v>
+        <v>0.6695312499999999</v>
       </c>
     </row>
     <row r="613">
@@ -5333,7 +5333,7 @@
         <v>612</v>
       </c>
       <c r="B613" t="n">
-        <v>0</v>
+        <v>0.71171875</v>
       </c>
     </row>
     <row r="614">
@@ -5341,7 +5341,7 @@
         <v>613</v>
       </c>
       <c r="B614" t="n">
-        <v>0.70609375</v>
+        <v>0.98171875</v>
       </c>
     </row>
     <row r="615">
@@ -5349,7 +5349,7 @@
         <v>614</v>
       </c>
       <c r="B615" t="n">
-        <v>0.6484375</v>
+        <v>0.49375</v>
       </c>
     </row>
     <row r="616">
@@ -5357,7 +5357,7 @@
         <v>615</v>
       </c>
       <c r="B616" t="n">
-        <v>0.600625</v>
+        <v>0.89734375</v>
       </c>
     </row>
     <row r="617">
@@ -5365,7 +5365,7 @@
         <v>616</v>
       </c>
       <c r="B617" t="n">
-        <v>0</v>
+        <v>0.308125</v>
       </c>
     </row>
     <row r="618">
@@ -5373,7 +5373,7 @@
         <v>617</v>
       </c>
       <c r="B618" t="n">
-        <v>0</v>
+        <v>0.9296875</v>
       </c>
     </row>
     <row r="619">
@@ -5381,7 +5381,7 @@
         <v>618</v>
       </c>
       <c r="B619" t="n">
-        <v>0</v>
+        <v>0.34609375</v>
       </c>
     </row>
     <row r="620">
@@ -5389,7 +5389,7 @@
         <v>619</v>
       </c>
       <c r="B620" t="n">
-        <v>0</v>
+        <v>0.95640625</v>
       </c>
     </row>
     <row r="621">
@@ -5397,7 +5397,7 @@
         <v>620</v>
       </c>
       <c r="B621" t="n">
-        <v>0.6526562499999999</v>
+        <v>0.59359375</v>
       </c>
     </row>
     <row r="622">
@@ -5405,7 +5405,7 @@
         <v>621</v>
       </c>
       <c r="B622" t="n">
-        <v>0.4332812500000001</v>
+        <v>0.5035937500000001</v>
       </c>
     </row>
     <row r="623">
@@ -5413,7 +5413,7 @@
         <v>622</v>
       </c>
       <c r="B623" t="n">
-        <v>0</v>
+        <v>0.6737500000000001</v>
       </c>
     </row>
     <row r="624">
@@ -5421,7 +5421,7 @@
         <v>623</v>
       </c>
       <c r="B624" t="n">
-        <v>0</v>
+        <v>0.94515625</v>
       </c>
     </row>
     <row r="625">
@@ -5429,7 +5429,7 @@
         <v>624</v>
       </c>
       <c r="B625" t="n">
-        <v>0</v>
+        <v>0.3643749999999999</v>
       </c>
     </row>
     <row r="626">
@@ -5437,7 +5437,7 @@
         <v>625</v>
       </c>
       <c r="B626" t="n">
-        <v>0.7229687499999999</v>
+        <v>0.80875</v>
       </c>
     </row>
     <row r="627">
@@ -5445,7 +5445,7 @@
         <v>626</v>
       </c>
       <c r="B627" t="n">
-        <v>0</v>
+        <v>0.81859375</v>
       </c>
     </row>
     <row r="628">
@@ -5453,7 +5453,7 @@
         <v>627</v>
       </c>
       <c r="B628" t="n">
-        <v>0</v>
+        <v>0.77640625</v>
       </c>
     </row>
     <row r="629">
@@ -5469,7 +5469,7 @@
         <v>629</v>
       </c>
       <c r="B630" t="n">
-        <v>0</v>
+        <v>0.39671875</v>
       </c>
     </row>
     <row r="631">
@@ -5477,7 +5477,7 @@
         <v>630</v>
       </c>
       <c r="B631" t="n">
-        <v>0.59078125</v>
+        <v>0.80734375</v>
       </c>
     </row>
     <row r="632">
@@ -5485,7 +5485,7 @@
         <v>631</v>
       </c>
       <c r="B632" t="n">
-        <v>0.94234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="633">
@@ -5493,7 +5493,7 @@
         <v>632</v>
       </c>
       <c r="B633" t="n">
-        <v>0.7778125</v>
+        <v>0.6709375</v>
       </c>
     </row>
     <row r="634">
@@ -5501,7 +5501,7 @@
         <v>633</v>
       </c>
       <c r="B634" t="n">
-        <v>0</v>
+        <v>0.86640625</v>
       </c>
     </row>
     <row r="635">
@@ -5509,7 +5509,7 @@
         <v>634</v>
       </c>
       <c r="B635" t="n">
-        <v>0</v>
+        <v>0.7201562500000001</v>
       </c>
     </row>
     <row r="636">
@@ -5517,7 +5517,7 @@
         <v>635</v>
       </c>
       <c r="B636" t="n">
-        <v>0</v>
+        <v>0.75671875</v>
       </c>
     </row>
     <row r="637">
@@ -5525,7 +5525,7 @@
         <v>636</v>
       </c>
       <c r="B637" t="n">
-        <v>0</v>
+        <v>0.88046875</v>
       </c>
     </row>
     <row r="638">
@@ -5533,7 +5533,7 @@
         <v>637</v>
       </c>
       <c r="B638" t="n">
-        <v>0.61890625</v>
+        <v>0.9296875</v>
       </c>
     </row>
     <row r="639">
@@ -5541,7 +5541,7 @@
         <v>638</v>
       </c>
       <c r="B639" t="n">
-        <v>0.6470312499999999</v>
+        <v>0.4740625000000001</v>
       </c>
     </row>
     <row r="640">
@@ -5549,7 +5549,7 @@
         <v>639</v>
       </c>
       <c r="B640" t="n">
-        <v>0.578125</v>
+        <v>0.37703125</v>
       </c>
     </row>
     <row r="641">
@@ -5573,7 +5573,7 @@
         <v>642</v>
       </c>
       <c r="B643" t="n">
-        <v>0</v>
+        <v>0.95921875</v>
       </c>
     </row>
     <row r="644">
@@ -5581,7 +5581,7 @@
         <v>643</v>
       </c>
       <c r="B644" t="n">
-        <v>0</v>
+        <v>0.926875</v>
       </c>
     </row>
     <row r="645">
@@ -5589,7 +5589,7 @@
         <v>644</v>
       </c>
       <c r="B645" t="n">
-        <v>0.6498437500000001</v>
+        <v>0.93953125</v>
       </c>
     </row>
     <row r="646">
@@ -5597,7 +5597,7 @@
         <v>645</v>
       </c>
       <c r="B646" t="n">
-        <v>0</v>
+        <v>0.9465625</v>
       </c>
     </row>
     <row r="647">
@@ -5605,7 +5605,7 @@
         <v>646</v>
       </c>
       <c r="B647" t="n">
-        <v>0</v>
+        <v>0.88046875</v>
       </c>
     </row>
     <row r="648">
@@ -5613,7 +5613,7 @@
         <v>647</v>
       </c>
       <c r="B648" t="n">
-        <v>0.55703125</v>
+        <v>0.9128125</v>
       </c>
     </row>
     <row r="649">
@@ -5621,7 +5621,7 @@
         <v>648</v>
       </c>
       <c r="B649" t="n">
-        <v>0</v>
+        <v>0.308125</v>
       </c>
     </row>
     <row r="650">
@@ -5629,7 +5629,7 @@
         <v>649</v>
       </c>
       <c r="B650" t="n">
-        <v>0</v>
+        <v>0.9071875</v>
       </c>
     </row>
     <row r="651">
@@ -5637,7 +5637,7 @@
         <v>650</v>
       </c>
       <c r="B651" t="n">
-        <v>0.9184375</v>
+        <v>0.34890625</v>
       </c>
     </row>
     <row r="652">
@@ -5645,7 +5645,7 @@
         <v>651</v>
       </c>
       <c r="B652" t="n">
-        <v>0</v>
+        <v>0.89171875</v>
       </c>
     </row>
     <row r="653">
@@ -5653,7 +5653,7 @@
         <v>652</v>
       </c>
       <c r="B653" t="n">
-        <v>0</v>
+        <v>0.7665625</v>
       </c>
     </row>
     <row r="654">
@@ -5661,7 +5661,7 @@
         <v>653</v>
       </c>
       <c r="B654" t="n">
-        <v>0.75953125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="655">
@@ -5669,7 +5669,7 @@
         <v>654</v>
       </c>
       <c r="B655" t="n">
-        <v>0.8903125000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="656">
@@ -5677,7 +5677,7 @@
         <v>655</v>
       </c>
       <c r="B656" t="n">
-        <v>0.80734375</v>
+        <v>0.6625</v>
       </c>
     </row>
     <row r="657">
@@ -5685,7 +5685,7 @@
         <v>656</v>
       </c>
       <c r="B657" t="n">
-        <v>0.56265625</v>
+        <v>0.82140625</v>
       </c>
     </row>
     <row r="658">
@@ -5693,7 +5693,7 @@
         <v>657</v>
       </c>
       <c r="B658" t="n">
-        <v>0.8171875</v>
+        <v>0.9296875</v>
       </c>
     </row>
     <row r="659">
@@ -5701,7 +5701,7 @@
         <v>658</v>
       </c>
       <c r="B659" t="n">
-        <v>0</v>
+        <v>0.9578125</v>
       </c>
     </row>
     <row r="660">
@@ -5709,7 +5709,7 @@
         <v>659</v>
       </c>
       <c r="B660" t="n">
-        <v>0.7285937499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="661">
@@ -5717,7 +5717,7 @@
         <v>660</v>
       </c>
       <c r="B661" t="n">
-        <v>0.82703125</v>
+        <v>0.4389062500000001</v>
       </c>
     </row>
     <row r="662">
@@ -5725,7 +5725,7 @@
         <v>661</v>
       </c>
       <c r="B662" t="n">
-        <v>0.83828125</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="663">
@@ -5733,7 +5733,7 @@
         <v>662</v>
       </c>
       <c r="B663" t="n">
-        <v>0</v>
+        <v>0.8340624999999999</v>
       </c>
     </row>
     <row r="664">
@@ -5741,7 +5741,7 @@
         <v>663</v>
       </c>
       <c r="B664" t="n">
-        <v>0</v>
+        <v>0.9296875</v>
       </c>
     </row>
     <row r="665">
@@ -5749,7 +5749,7 @@
         <v>664</v>
       </c>
       <c r="B665" t="n">
-        <v>0.8171875</v>
+        <v>0.8396875</v>
       </c>
     </row>
     <row r="666">
@@ -5757,7 +5757,7 @@
         <v>665</v>
       </c>
       <c r="B666" t="n">
-        <v>0.4698437499999999</v>
+        <v>0.76796875</v>
       </c>
     </row>
     <row r="667">
@@ -5765,7 +5765,7 @@
         <v>666</v>
       </c>
       <c r="B667" t="n">
-        <v>0.7103124999999999</v>
+        <v>0.4445312499999999</v>
       </c>
     </row>
     <row r="668">
@@ -5773,7 +5773,7 @@
         <v>667</v>
       </c>
       <c r="B668" t="n">
-        <v>0</v>
+        <v>0.69203125</v>
       </c>
     </row>
     <row r="669">
@@ -5781,7 +5781,7 @@
         <v>668</v>
       </c>
       <c r="B669" t="n">
-        <v>0</v>
+        <v>0.9746875</v>
       </c>
     </row>
     <row r="670">
@@ -5789,7 +5789,7 @@
         <v>669</v>
       </c>
       <c r="B670" t="n">
-        <v>0.87765625</v>
+        <v>0.90859375</v>
       </c>
     </row>
     <row r="671">
@@ -5797,7 +5797,7 @@
         <v>670</v>
       </c>
       <c r="B671" t="n">
-        <v>0.7904687500000001</v>
+        <v>0.9353125</v>
       </c>
     </row>
     <row r="672">
@@ -5805,7 +5805,7 @@
         <v>671</v>
       </c>
       <c r="B672" t="n">
-        <v>0.5190625</v>
+        <v>0.6118749999999999</v>
       </c>
     </row>
     <row r="673">
@@ -5813,7 +5813,7 @@
         <v>672</v>
       </c>
       <c r="B673" t="n">
-        <v>0.4445312499999999</v>
+        <v>0.95921875</v>
       </c>
     </row>
     <row r="674">
@@ -5821,7 +5821,7 @@
         <v>673</v>
       </c>
       <c r="B674" t="n">
-        <v>0</v>
+        <v>0.7553125000000001</v>
       </c>
     </row>
     <row r="675">
@@ -5829,7 +5829,7 @@
         <v>674</v>
       </c>
       <c r="B675" t="n">
-        <v>0</v>
+        <v>0.938125</v>
       </c>
     </row>
     <row r="676">
@@ -5837,7 +5837,7 @@
         <v>675</v>
       </c>
       <c r="B676" t="n">
-        <v>0.6231249999999999</v>
+        <v>0.83265625</v>
       </c>
     </row>
     <row r="677">
@@ -5845,7 +5845,7 @@
         <v>676</v>
       </c>
       <c r="B677" t="n">
-        <v>0.7271875</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="678">
@@ -5853,7 +5853,7 @@
         <v>677</v>
       </c>
       <c r="B678" t="n">
-        <v>0.6709375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="679">
@@ -5861,7 +5861,7 @@
         <v>678</v>
       </c>
       <c r="B679" t="n">
-        <v>0.30671875</v>
+        <v>0.38265625</v>
       </c>
     </row>
     <row r="680">
@@ -5869,7 +5869,7 @@
         <v>679</v>
       </c>
       <c r="B680" t="n">
-        <v>0.75390625</v>
+        <v>0.5978125</v>
       </c>
     </row>
     <row r="681">
@@ -5877,7 +5877,7 @@
         <v>680</v>
       </c>
       <c r="B681" t="n">
-        <v>0</v>
+        <v>0.6625</v>
       </c>
     </row>
     <row r="682">
@@ -5885,7 +5885,7 @@
         <v>681</v>
       </c>
       <c r="B682" t="n">
-        <v>0.75953125</v>
+        <v>0.9015625</v>
       </c>
     </row>
     <row r="683">
@@ -5893,7 +5893,7 @@
         <v>682</v>
       </c>
       <c r="B683" t="n">
-        <v>0.341875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="684">
@@ -5901,7 +5901,7 @@
         <v>683</v>
       </c>
       <c r="B684" t="n">
-        <v>0</v>
+        <v>0.82703125</v>
       </c>
     </row>
     <row r="685">
@@ -5909,7 +5909,7 @@
         <v>684</v>
       </c>
       <c r="B685" t="n">
-        <v>0.4459375</v>
+        <v>0.89171875</v>
       </c>
     </row>
     <row r="686">
@@ -5917,7 +5917,7 @@
         <v>685</v>
       </c>
       <c r="B686" t="n">
-        <v>0.62171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="687">
@@ -5925,7 +5925,7 @@
         <v>686</v>
       </c>
       <c r="B687" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="688">
@@ -5933,7 +5933,7 @@
         <v>687</v>
       </c>
       <c r="B688" t="n">
-        <v>0.70046875</v>
+        <v>0.9128125</v>
       </c>
     </row>
     <row r="689">
@@ -5941,7 +5941,7 @@
         <v>688</v>
       </c>
       <c r="B689" t="n">
-        <v>0</v>
+        <v>0.2982812500000001</v>
       </c>
     </row>
     <row r="690">
@@ -5949,7 +5949,7 @@
         <v>689</v>
       </c>
       <c r="B690" t="n">
-        <v>0.8495312500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="691">
@@ -5957,7 +5957,7 @@
         <v>690</v>
       </c>
       <c r="B691" t="n">
-        <v>0.521875</v>
+        <v>0.73421875</v>
       </c>
     </row>
     <row r="692">
@@ -5965,7 +5965,7 @@
         <v>691</v>
       </c>
       <c r="B692" t="n">
-        <v>0.386875</v>
+        <v>0.88890625</v>
       </c>
     </row>
     <row r="693">
@@ -5973,7 +5973,7 @@
         <v>692</v>
       </c>
       <c r="B693" t="n">
-        <v>0.78484375</v>
+        <v>0.90015625</v>
       </c>
     </row>
     <row r="694">
@@ -5981,7 +5981,7 @@
         <v>693</v>
       </c>
       <c r="B694" t="n">
-        <v>0.7637499999999999</v>
+        <v>0.93671875</v>
       </c>
     </row>
     <row r="695">
@@ -5989,7 +5989,7 @@
         <v>694</v>
       </c>
       <c r="B695" t="n">
-        <v>0.926875</v>
+        <v>0.9282812499999999</v>
       </c>
     </row>
     <row r="696">
@@ -5997,7 +5997,7 @@
         <v>695</v>
       </c>
       <c r="B696" t="n">
-        <v>0.431875</v>
+        <v>0.76515625</v>
       </c>
     </row>
     <row r="697">
@@ -6005,7 +6005,7 @@
         <v>696</v>
       </c>
       <c r="B697" t="n">
-        <v>0.7975</v>
+        <v>0.78484375</v>
       </c>
     </row>
     <row r="698">
@@ -6021,7 +6021,7 @@
         <v>698</v>
       </c>
       <c r="B699" t="n">
-        <v>0.3685937500000001</v>
+        <v>0.34046875</v>
       </c>
     </row>
     <row r="700">
@@ -6029,7 +6029,7 @@
         <v>699</v>
       </c>
       <c r="B700" t="n">
-        <v>0</v>
+        <v>0.81015625</v>
       </c>
     </row>
     <row r="701">
@@ -6037,7 +6037,7 @@
         <v>700</v>
       </c>
       <c r="B701" t="n">
-        <v>0</v>
+        <v>0.9634374999999999</v>
       </c>
     </row>
     <row r="702">
@@ -6045,7 +6045,7 @@
         <v>701</v>
       </c>
       <c r="B702" t="n">
-        <v>0.77640625</v>
+        <v>0.84109375</v>
       </c>
     </row>
     <row r="703">
@@ -6053,7 +6053,7 @@
         <v>702</v>
       </c>
       <c r="B703" t="n">
-        <v>0.3714062499999999</v>
+        <v>0.97046875</v>
       </c>
     </row>
     <row r="704">
@@ -6061,7 +6061,7 @@
         <v>703</v>
       </c>
       <c r="B704" t="n">
-        <v>0.8059375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="705">
@@ -6069,7 +6069,7 @@
         <v>704</v>
       </c>
       <c r="B705" t="n">
-        <v>0.2982812500000001</v>
+        <v>0.960625</v>
       </c>
     </row>
     <row r="706">
@@ -6077,7 +6077,7 @@
         <v>705</v>
       </c>
       <c r="B706" t="n">
-        <v>0.5992187499999999</v>
+        <v>0.859375</v>
       </c>
     </row>
     <row r="707">
@@ -6085,7 +6085,7 @@
         <v>706</v>
       </c>
       <c r="B707" t="n">
-        <v>0</v>
+        <v>0.83828125</v>
       </c>
     </row>
     <row r="708">
@@ -6093,7 +6093,7 @@
         <v>707</v>
       </c>
       <c r="B708" t="n">
-        <v>0.7721875</v>
+        <v>0.8692187499999999</v>
       </c>
     </row>
     <row r="709">
@@ -6101,7 +6101,7 @@
         <v>708</v>
       </c>
       <c r="B709" t="n">
-        <v>0.8171875</v>
+        <v>0.8692187499999999</v>
       </c>
     </row>
     <row r="710">
@@ -6117,7 +6117,7 @@
         <v>710</v>
       </c>
       <c r="B711" t="n">
-        <v>0</v>
+        <v>0.42625</v>
       </c>
     </row>
     <row r="712">
@@ -6125,7 +6125,7 @@
         <v>711</v>
       </c>
       <c r="B712" t="n">
-        <v>0.42625</v>
+        <v>0.80734375</v>
       </c>
     </row>
     <row r="713">
@@ -6133,7 +6133,7 @@
         <v>712</v>
       </c>
       <c r="B713" t="n">
-        <v>0.9296875</v>
+        <v>0.5049999999999999</v>
       </c>
     </row>
     <row r="714">
@@ -6141,7 +6141,7 @@
         <v>713</v>
       </c>
       <c r="B714" t="n">
-        <v>0.73</v>
+        <v>0.69484375</v>
       </c>
     </row>
     <row r="715">
@@ -6149,7 +6149,7 @@
         <v>714</v>
       </c>
       <c r="B715" t="n">
-        <v>0.77359375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="716">
@@ -6157,7 +6157,7 @@
         <v>715</v>
       </c>
       <c r="B716" t="n">
-        <v>0.7665625</v>
+        <v>0.82140625</v>
       </c>
     </row>
     <row r="717">
@@ -6165,7 +6165,7 @@
         <v>716</v>
       </c>
       <c r="B717" t="n">
-        <v>0.5134375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="718">
@@ -6173,7 +6173,7 @@
         <v>717</v>
       </c>
       <c r="B718" t="n">
-        <v>0.69484375</v>
+        <v>0.81578125</v>
       </c>
     </row>
     <row r="719">
@@ -6181,7 +6181,7 @@
         <v>718</v>
       </c>
       <c r="B719" t="n">
-        <v>0.9015625</v>
+        <v>0.56125</v>
       </c>
     </row>
     <row r="720">
@@ -6189,7 +6189,7 @@
         <v>719</v>
       </c>
       <c r="B720" t="n">
-        <v>0.77359375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="721">
@@ -6197,7 +6197,7 @@
         <v>720</v>
       </c>
       <c r="B721" t="n">
-        <v>0.76515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="722">
@@ -6205,7 +6205,7 @@
         <v>721</v>
       </c>
       <c r="B722" t="n">
-        <v>0.82140625</v>
+        <v>0.96484375</v>
       </c>
     </row>
     <row r="723">
@@ -6213,7 +6213,7 @@
         <v>722</v>
       </c>
       <c r="B723" t="n">
-        <v>0</v>
+        <v>0.803125</v>
       </c>
     </row>
     <row r="724">
@@ -6221,7 +6221,7 @@
         <v>723</v>
       </c>
       <c r="B724" t="n">
-        <v>0.60625</v>
+        <v>0.67796875</v>
       </c>
     </row>
     <row r="725">
@@ -6229,7 +6229,7 @@
         <v>724</v>
       </c>
       <c r="B725" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="726">
@@ -6237,7 +6237,7 @@
         <v>725</v>
       </c>
       <c r="B726" t="n">
-        <v>0</v>
+        <v>0.9015625</v>
       </c>
     </row>
     <row r="727">
@@ -6245,7 +6245,7 @@
         <v>726</v>
       </c>
       <c r="B727" t="n">
-        <v>0</v>
+        <v>0.8607812500000001</v>
       </c>
     </row>
     <row r="728">
@@ -6253,7 +6253,7 @@
         <v>727</v>
       </c>
       <c r="B728" t="n">
-        <v>0.74265625</v>
+        <v>0.859375</v>
       </c>
     </row>
     <row r="729">
@@ -6261,7 +6261,7 @@
         <v>728</v>
       </c>
       <c r="B729" t="n">
-        <v>0.83125</v>
+        <v>0.8987499999999999</v>
       </c>
     </row>
     <row r="730">
@@ -6269,7 +6269,7 @@
         <v>729</v>
       </c>
       <c r="B730" t="n">
-        <v>0.8171875</v>
+        <v>0.6231249999999999</v>
       </c>
     </row>
     <row r="731">
@@ -6277,7 +6277,7 @@
         <v>730</v>
       </c>
       <c r="B731" t="n">
-        <v>0.915625</v>
+        <v>0.8635937499999999</v>
       </c>
     </row>
     <row r="732">
@@ -6285,7 +6285,7 @@
         <v>731</v>
       </c>
       <c r="B732" t="n">
-        <v>0</v>
+        <v>0.8425</v>
       </c>
     </row>
     <row r="733">
@@ -6293,7 +6293,7 @@
         <v>732</v>
       </c>
       <c r="B733" t="n">
-        <v>0.59078125</v>
+        <v>0.94375</v>
       </c>
     </row>
     <row r="734">
@@ -6301,7 +6301,7 @@
         <v>733</v>
       </c>
       <c r="B734" t="n">
-        <v>0.55421875</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="735">
@@ -6309,7 +6309,7 @@
         <v>734</v>
       </c>
       <c r="B735" t="n">
-        <v>0.69484375</v>
+        <v>0.69625</v>
       </c>
     </row>
     <row r="736">
@@ -6317,7 +6317,7 @@
         <v>735</v>
       </c>
       <c r="B736" t="n">
-        <v>0</v>
+        <v>0.5921875</v>
       </c>
     </row>
     <row r="737">
@@ -6325,7 +6325,7 @@
         <v>736</v>
       </c>
       <c r="B737" t="n">
-        <v>0.4290625</v>
+        <v>0.7609375</v>
       </c>
     </row>
     <row r="738">
@@ -6333,7 +6333,7 @@
         <v>737</v>
       </c>
       <c r="B738" t="n">
-        <v>0</v>
+        <v>0.848125</v>
       </c>
     </row>
     <row r="739">
@@ -6341,7 +6341,7 @@
         <v>738</v>
       </c>
       <c r="B739" t="n">
-        <v>0</v>
+        <v>0.61609375</v>
       </c>
     </row>
     <row r="740">
@@ -6349,7 +6349,7 @@
         <v>739</v>
       </c>
       <c r="B740" t="n">
-        <v>0.3643749999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="741">
@@ -6357,7 +6357,7 @@
         <v>740</v>
       </c>
       <c r="B741" t="n">
-        <v>0.51765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="742">
@@ -6365,7 +6365,7 @@
         <v>741</v>
       </c>
       <c r="B742" t="n">
-        <v>0.87625</v>
+        <v>0.96765625</v>
       </c>
     </row>
     <row r="743">
@@ -6381,7 +6381,7 @@
         <v>743</v>
       </c>
       <c r="B744" t="n">
-        <v>0</v>
+        <v>0.85375</v>
       </c>
     </row>
     <row r="745">
@@ -6389,7 +6389,7 @@
         <v>744</v>
       </c>
       <c r="B745" t="n">
-        <v>0</v>
+        <v>0.7932812499999999</v>
       </c>
     </row>
     <row r="746">
@@ -6397,7 +6397,7 @@
         <v>745</v>
       </c>
       <c r="B746" t="n">
-        <v>0.3981250000000001</v>
+        <v>0.971875</v>
       </c>
     </row>
     <row r="747">
@@ -6405,7 +6405,7 @@
         <v>746</v>
       </c>
       <c r="B747" t="n">
-        <v>0.7285937499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="748">
@@ -6413,7 +6413,7 @@
         <v>747</v>
       </c>
       <c r="B748" t="n">
-        <v>0.84109375</v>
+        <v>0.79609375</v>
       </c>
     </row>
     <row r="749">
@@ -6429,7 +6429,7 @@
         <v>749</v>
       </c>
       <c r="B750" t="n">
-        <v>0.88328125</v>
+        <v>0.870625</v>
       </c>
     </row>
     <row r="751">
@@ -6437,7 +6437,7 @@
         <v>750</v>
       </c>
       <c r="B751" t="n">
-        <v>0.68078125</v>
+        <v>0.68359375</v>
       </c>
     </row>
     <row r="752">
@@ -6453,7 +6453,7 @@
         <v>752</v>
       </c>
       <c r="B753" t="n">
-        <v>0</v>
+        <v>0.8340624999999999</v>
       </c>
     </row>
     <row r="754">
@@ -6461,7 +6461,7 @@
         <v>753</v>
       </c>
       <c r="B754" t="n">
-        <v>0.85234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="755">
@@ -6469,7 +6469,7 @@
         <v>754</v>
       </c>
       <c r="B755" t="n">
-        <v>0.7581249999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="756">
@@ -6477,7 +6477,7 @@
         <v>755</v>
       </c>
       <c r="B756" t="n">
-        <v>0.9128125</v>
+        <v>0.75953125</v>
       </c>
     </row>
     <row r="757">
@@ -6485,7 +6485,7 @@
         <v>756</v>
       </c>
       <c r="B757" t="n">
-        <v>0.595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="758">
@@ -6493,7 +6493,7 @@
         <v>757</v>
       </c>
       <c r="B758" t="n">
-        <v>0.48671875</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="759">
@@ -6501,7 +6501,7 @@
         <v>758</v>
       </c>
       <c r="B759" t="n">
-        <v>0.63015625</v>
+        <v>0.70328125</v>
       </c>
     </row>
     <row r="760">
@@ -6509,7 +6509,7 @@
         <v>759</v>
       </c>
       <c r="B760" t="n">
-        <v>0.75953125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="761">
@@ -6517,7 +6517,7 @@
         <v>760</v>
       </c>
       <c r="B761" t="n">
-        <v>0.5584375</v>
+        <v>0.938125</v>
       </c>
     </row>
     <row r="762">
@@ -6525,7 +6525,7 @@
         <v>761</v>
       </c>
       <c r="B762" t="n">
-        <v>0.97609375</v>
+        <v>0.95921875</v>
       </c>
     </row>
     <row r="763">
@@ -6533,7 +6533,7 @@
         <v>762</v>
       </c>
       <c r="B763" t="n">
-        <v>0.35734375</v>
+        <v>0.97890625</v>
       </c>
     </row>
     <row r="764">
@@ -6541,7 +6541,7 @@
         <v>763</v>
       </c>
       <c r="B764" t="n">
-        <v>0.8607812500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="765">
@@ -6549,7 +6549,7 @@
         <v>764</v>
       </c>
       <c r="B765" t="n">
-        <v>0</v>
+        <v>0.8003125</v>
       </c>
     </row>
     <row r="766">
@@ -6557,7 +6557,7 @@
         <v>765</v>
       </c>
       <c r="B766" t="n">
-        <v>0.7328125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="767">
@@ -6565,7 +6565,7 @@
         <v>766</v>
       </c>
       <c r="B767" t="n">
-        <v>0.88328125</v>
+        <v>0.578125</v>
       </c>
     </row>
     <row r="768">
@@ -6573,7 +6573,7 @@
         <v>767</v>
       </c>
       <c r="B768" t="n">
-        <v>0.9310937500000001</v>
+        <v>0.8635937499999999</v>
       </c>
     </row>
     <row r="769">
@@ -6581,7 +6581,7 @@
         <v>768</v>
       </c>
       <c r="B769" t="n">
-        <v>0.61046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="770">
@@ -6589,7 +6589,7 @@
         <v>769</v>
       </c>
       <c r="B770" t="n">
-        <v>0.5992187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="771">
@@ -6597,7 +6597,7 @@
         <v>770</v>
       </c>
       <c r="B771" t="n">
-        <v>0.77640625</v>
+        <v>0.82421875</v>
       </c>
     </row>
     <row r="772">
@@ -6605,7 +6605,7 @@
         <v>771</v>
       </c>
       <c r="B772" t="n">
-        <v>0.7890625</v>
+        <v>0.95640625</v>
       </c>
     </row>
     <row r="773">
@@ -6613,7 +6613,7 @@
         <v>772</v>
       </c>
       <c r="B773" t="n">
-        <v>0.3165625</v>
+        <v>0.7384375</v>
       </c>
     </row>
     <row r="774">
@@ -6621,7 +6621,7 @@
         <v>773</v>
       </c>
       <c r="B774" t="n">
-        <v>0.4459375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="775">
@@ -6629,7 +6629,7 @@
         <v>774</v>
       </c>
       <c r="B775" t="n">
-        <v>0</v>
+        <v>0.960625</v>
       </c>
     </row>
     <row r="776">
@@ -6637,7 +6637,7 @@
         <v>775</v>
       </c>
       <c r="B776" t="n">
-        <v>0.39390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="777">
@@ -6645,7 +6645,7 @@
         <v>776</v>
       </c>
       <c r="B777" t="n">
-        <v>0.47265625</v>
+        <v>0.8284374999999999</v>
       </c>
     </row>
     <row r="778">
@@ -6661,7 +6661,7 @@
         <v>778</v>
       </c>
       <c r="B779" t="n">
-        <v>0.6442187500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="780">
@@ -6669,7 +6669,7 @@
         <v>779</v>
       </c>
       <c r="B780" t="n">
-        <v>0</v>
+        <v>0.8171875</v>
       </c>
     </row>
     <row r="781">
@@ -6677,7 +6677,7 @@
         <v>780</v>
       </c>
       <c r="B781" t="n">
-        <v>0</v>
+        <v>0.4909374999999999</v>
       </c>
     </row>
     <row r="782">
@@ -6685,7 +6685,7 @@
         <v>781</v>
       </c>
       <c r="B782" t="n">
-        <v>0</v>
+        <v>0.971875</v>
       </c>
     </row>
     <row r="783">
@@ -6693,7 +6693,7 @@
         <v>782</v>
       </c>
       <c r="B783" t="n">
-        <v>0.42625</v>
+        <v>0.3503124999999999</v>
       </c>
     </row>
     <row r="784">
@@ -6701,7 +6701,7 @@
         <v>783</v>
       </c>
       <c r="B784" t="n">
-        <v>0.9015625</v>
+        <v>0.71171875</v>
       </c>
     </row>
     <row r="785">
@@ -6709,7 +6709,7 @@
         <v>784</v>
       </c>
       <c r="B785" t="n">
-        <v>0</v>
+        <v>0.9521875</v>
       </c>
     </row>
     <row r="786">
@@ -6717,7 +6717,7 @@
         <v>785</v>
       </c>
       <c r="B786" t="n">
-        <v>0</v>
+        <v>0.8692187499999999</v>
       </c>
     </row>
     <row r="787">
@@ -6725,7 +6725,7 @@
         <v>786</v>
       </c>
       <c r="B787" t="n">
-        <v>0.96484375</v>
+        <v>0.84671875</v>
       </c>
     </row>
     <row r="788">
@@ -6733,7 +6733,7 @@
         <v>787</v>
       </c>
       <c r="B788" t="n">
-        <v>0.71171875</v>
+        <v>0.9184375</v>
       </c>
     </row>
     <row r="789">
@@ -6741,7 +6741,7 @@
         <v>788</v>
       </c>
       <c r="B789" t="n">
-        <v>0</v>
+        <v>0.5528124999999999</v>
       </c>
     </row>
     <row r="790">
@@ -6749,7 +6749,7 @@
         <v>789</v>
       </c>
       <c r="B790" t="n">
-        <v>0.82140625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="791">
@@ -6757,7 +6757,7 @@
         <v>790</v>
       </c>
       <c r="B791" t="n">
-        <v>0.7173437499999999</v>
+        <v>0.9465625</v>
       </c>
     </row>
     <row r="792">
@@ -6765,7 +6765,7 @@
         <v>791</v>
       </c>
       <c r="B792" t="n">
-        <v>0.8509375</v>
+        <v>0.93671875</v>
       </c>
     </row>
     <row r="793">
@@ -6773,7 +6773,7 @@
         <v>792</v>
       </c>
       <c r="B793" t="n">
-        <v>0.9071875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="794">
@@ -6781,7 +6781,7 @@
         <v>793</v>
       </c>
       <c r="B794" t="n">
-        <v>0.8987499999999999</v>
+        <v>0.84390625</v>
       </c>
     </row>
     <row r="795">
@@ -6789,7 +6789,7 @@
         <v>794</v>
       </c>
       <c r="B795" t="n">
-        <v>0.5809375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="796">
@@ -6797,7 +6797,7 @@
         <v>795</v>
       </c>
       <c r="B796" t="n">
-        <v>0.9465625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="797">
@@ -6805,7 +6805,7 @@
         <v>796</v>
       </c>
       <c r="B797" t="n">
-        <v>0.90296875</v>
+        <v>0.97046875</v>
       </c>
     </row>
     <row r="798">
@@ -6813,7 +6813,7 @@
         <v>797</v>
       </c>
       <c r="B798" t="n">
-        <v>0.6442187500000001</v>
+        <v>0.8171875</v>
       </c>
     </row>
     <row r="799">
@@ -6821,7 +6821,7 @@
         <v>798</v>
       </c>
       <c r="B799" t="n">
-        <v>0.960625</v>
+        <v>0.8143750000000001</v>
       </c>
     </row>
     <row r="800">
@@ -6829,7 +6829,7 @@
         <v>799</v>
       </c>
       <c r="B800" t="n">
-        <v>0.3306249999999999</v>
+        <v>0.8059375</v>
       </c>
     </row>
     <row r="801">
@@ -6845,7 +6845,7 @@
         <v>801</v>
       </c>
       <c r="B802" t="n">
-        <v>0.865</v>
+        <v>0.87484375</v>
       </c>
     </row>
     <row r="803">
@@ -6853,7 +6853,7 @@
         <v>802</v>
       </c>
       <c r="B803" t="n">
-        <v>0.90296875</v>
+        <v>0.8171875</v>
       </c>
     </row>
     <row r="804">
@@ -6861,7 +6861,7 @@
         <v>803</v>
       </c>
       <c r="B804" t="n">
-        <v>0.70046875</v>
+        <v>0.9015625</v>
       </c>
     </row>
     <row r="805">
@@ -6869,7 +6869,7 @@
         <v>804</v>
       </c>
       <c r="B805" t="n">
-        <v>0.92125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="806">
@@ -6877,7 +6877,7 @@
         <v>805</v>
       </c>
       <c r="B806" t="n">
-        <v>0.848125</v>
+        <v>0.9465625</v>
       </c>
     </row>
     <row r="807">
@@ -6885,7 +6885,7 @@
         <v>806</v>
       </c>
       <c r="B807" t="n">
-        <v>0.94234375</v>
+        <v>0.6582812499999999</v>
       </c>
     </row>
     <row r="808">
@@ -6893,7 +6893,7 @@
         <v>807</v>
       </c>
       <c r="B808" t="n">
-        <v>0</v>
+        <v>0.90578125</v>
       </c>
     </row>
     <row r="809">
@@ -6901,7 +6901,7 @@
         <v>808</v>
       </c>
       <c r="B809" t="n">
-        <v>0.85515625</v>
+        <v>0.96203125</v>
       </c>
     </row>
     <row r="810">
@@ -6909,7 +6909,7 @@
         <v>809</v>
       </c>
       <c r="B810" t="n">
-        <v>0.89453125</v>
+        <v>0.95640625</v>
       </c>
     </row>
     <row r="811">
@@ -6917,7 +6917,7 @@
         <v>810</v>
       </c>
       <c r="B811" t="n">
-        <v>0.9184375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="812">
@@ -6925,7 +6925,7 @@
         <v>811</v>
       </c>
       <c r="B812" t="n">
-        <v>0.9310937500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="813">
@@ -6933,7 +6933,7 @@
         <v>812</v>
       </c>
       <c r="B813" t="n">
-        <v>0.67234375</v>
+        <v>0.93671875</v>
       </c>
     </row>
     <row r="814">
@@ -6941,7 +6941,7 @@
         <v>813</v>
       </c>
       <c r="B814" t="n">
-        <v>0.36015625</v>
+        <v>0.93953125</v>
       </c>
     </row>
     <row r="815">
@@ -6949,7 +6949,7 @@
         <v>814</v>
       </c>
       <c r="B815" t="n">
-        <v>0.88890625</v>
+        <v>0.78203125</v>
       </c>
     </row>
     <row r="816">
@@ -6965,7 +6965,7 @@
         <v>816</v>
       </c>
       <c r="B817" t="n">
-        <v>0</v>
+        <v>0.791875</v>
       </c>
     </row>
     <row r="818">
@@ -6973,7 +6973,7 @@
         <v>817</v>
       </c>
       <c r="B818" t="n">
-        <v>0.65125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="819">
@@ -6981,7 +6981,7 @@
         <v>818</v>
       </c>
       <c r="B819" t="n">
-        <v>0</v>
+        <v>0.4853124999999999</v>
       </c>
     </row>
     <row r="820">
@@ -6989,7 +6989,7 @@
         <v>819</v>
       </c>
       <c r="B820" t="n">
-        <v>0.5134375</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="821">
@@ -6997,7 +6997,7 @@
         <v>820</v>
       </c>
       <c r="B821" t="n">
-        <v>0.9325</v>
+        <v>0.9240625</v>
       </c>
     </row>
     <row r="822">
@@ -7013,7 +7013,7 @@
         <v>822</v>
       </c>
       <c r="B823" t="n">
-        <v>0.690625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="824">
@@ -7021,7 +7021,7 @@
         <v>823</v>
       </c>
       <c r="B824" t="n">
-        <v>0</v>
+        <v>0.74828125</v>
       </c>
     </row>
     <row r="825">
@@ -7029,7 +7029,7 @@
         <v>824</v>
       </c>
       <c r="B825" t="n">
-        <v>0.91703125</v>
+        <v>0.454375</v>
       </c>
     </row>
     <row r="826">
@@ -7037,7 +7037,7 @@
         <v>825</v>
       </c>
       <c r="B826" t="n">
-        <v>0.55703125</v>
+        <v>0.95640625</v>
       </c>
     </row>
     <row r="827">
@@ -7045,7 +7045,7 @@
         <v>826</v>
       </c>
       <c r="B827" t="n">
-        <v>0</v>
+        <v>0.926875</v>
       </c>
     </row>
     <row r="828">
@@ -7053,7 +7053,7 @@
         <v>827</v>
       </c>
       <c r="B828" t="n">
-        <v>0.4712499999999999</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="829">
@@ -7061,7 +7061,7 @@
         <v>828</v>
       </c>
       <c r="B829" t="n">
-        <v>0.93671875</v>
+        <v>0.96203125</v>
       </c>
     </row>
     <row r="830">
@@ -7069,7 +7069,7 @@
         <v>829</v>
       </c>
       <c r="B830" t="n">
-        <v>0</v>
+        <v>0.8256250000000001</v>
       </c>
     </row>
     <row r="831">
@@ -7077,7 +7077,7 @@
         <v>830</v>
       </c>
       <c r="B831" t="n">
-        <v>0.9578125</v>
+        <v>0.33765625</v>
       </c>
     </row>
     <row r="832">
@@ -7085,7 +7085,7 @@
         <v>831</v>
       </c>
       <c r="B832" t="n">
-        <v>0</v>
+        <v>0.9296875</v>
       </c>
     </row>
     <row r="833">
@@ -7093,7 +7093,7 @@
         <v>832</v>
       </c>
       <c r="B833" t="n">
-        <v>0</v>
+        <v>0.9465625</v>
       </c>
     </row>
     <row r="834">
@@ -7109,7 +7109,7 @@
         <v>834</v>
       </c>
       <c r="B835" t="n">
-        <v>0.37703125</v>
+        <v>0.960625</v>
       </c>
     </row>
     <row r="836">
@@ -7117,7 +7117,7 @@
         <v>835</v>
       </c>
       <c r="B836" t="n">
-        <v>0</v>
+        <v>0.8425</v>
       </c>
     </row>
     <row r="837">
@@ -7133,7 +7133,7 @@
         <v>837</v>
       </c>
       <c r="B838" t="n">
-        <v>0.7229687499999999</v>
+        <v>0.9662500000000001</v>
       </c>
     </row>
     <row r="839">
@@ -7141,7 +7141,7 @@
         <v>838</v>
       </c>
       <c r="B839" t="n">
-        <v>0.983125</v>
+        <v>0.98171875</v>
       </c>
     </row>
     <row r="840">
@@ -7157,7 +7157,7 @@
         <v>840</v>
       </c>
       <c r="B841" t="n">
-        <v>0</v>
+        <v>0.6695312499999999</v>
       </c>
     </row>
     <row r="842">
@@ -7173,7 +7173,7 @@
         <v>842</v>
       </c>
       <c r="B843" t="n">
-        <v>0.8340624999999999</v>
+        <v>0.95359375</v>
       </c>
     </row>
     <row r="844">
@@ -7181,7 +7181,7 @@
         <v>843</v>
       </c>
       <c r="B844" t="n">
-        <v>0.40515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="845">
@@ -7189,7 +7189,7 @@
         <v>844</v>
       </c>
       <c r="B845" t="n">
-        <v>0</v>
+        <v>0.94515625</v>
       </c>
     </row>
     <row r="846">
@@ -7197,7 +7197,7 @@
         <v>845</v>
       </c>
       <c r="B846" t="n">
-        <v>0</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="847">
@@ -7205,7 +7205,7 @@
         <v>846</v>
       </c>
       <c r="B847" t="n">
-        <v>0.9240625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="848">
@@ -7213,7 +7213,7 @@
         <v>847</v>
       </c>
       <c r="B848" t="n">
-        <v>0.6259375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="849">
@@ -7221,7 +7221,7 @@
         <v>848</v>
       </c>
       <c r="B849" t="n">
-        <v>0.97609375</v>
+        <v>0.690625</v>
       </c>
     </row>
     <row r="850">
@@ -7229,7 +7229,7 @@
         <v>849</v>
       </c>
       <c r="B850" t="n">
-        <v>0.88890625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="851">
@@ -7237,7 +7237,7 @@
         <v>850</v>
       </c>
       <c r="B851" t="n">
-        <v>0.8959375000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="852">
@@ -7245,7 +7245,7 @@
         <v>851</v>
       </c>
       <c r="B852" t="n">
-        <v>0.8987499999999999</v>
+        <v>0.61609375</v>
       </c>
     </row>
     <row r="853">
@@ -7253,7 +7253,7 @@
         <v>852</v>
       </c>
       <c r="B853" t="n">
-        <v>0.66390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="854">
@@ -7261,7 +7261,7 @@
         <v>853</v>
       </c>
       <c r="B854" t="n">
-        <v>0.780625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="855">
@@ -7269,7 +7269,7 @@
         <v>854</v>
       </c>
       <c r="B855" t="n">
-        <v>0</v>
+        <v>0.9521875</v>
       </c>
     </row>
     <row r="856">
@@ -7285,7 +7285,7 @@
         <v>856</v>
       </c>
       <c r="B857" t="n">
-        <v>0.97328125</v>
+        <v>0.73140625</v>
       </c>
     </row>
     <row r="858">
@@ -7293,7 +7293,7 @@
         <v>857</v>
       </c>
       <c r="B858" t="n">
-        <v>0.86640625</v>
+        <v>0.9521875</v>
       </c>
     </row>
     <row r="859">
@@ -7301,7 +7301,7 @@
         <v>858</v>
       </c>
       <c r="B859" t="n">
-        <v>0.6751562499999999</v>
+        <v>0.94515625</v>
       </c>
     </row>
     <row r="860">
@@ -7309,7 +7309,7 @@
         <v>859</v>
       </c>
       <c r="B860" t="n">
-        <v>0.91421875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="861">
@@ -7317,7 +7317,7 @@
         <v>860</v>
       </c>
       <c r="B861" t="n">
-        <v>0.971875</v>
+        <v>0.96484375</v>
       </c>
     </row>
     <row r="862">
@@ -7325,7 +7325,7 @@
         <v>861</v>
       </c>
       <c r="B862" t="n">
-        <v>0.6428125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="863">
@@ -7333,7 +7333,7 @@
         <v>862</v>
       </c>
       <c r="B863" t="n">
-        <v>0.82</v>
+        <v>0.90859375</v>
       </c>
     </row>
     <row r="864">
@@ -7341,7 +7341,7 @@
         <v>863</v>
       </c>
       <c r="B864" t="n">
-        <v>0.94234375</v>
+        <v>0.9690625</v>
       </c>
     </row>
     <row r="865">
@@ -7349,7 +7349,7 @@
         <v>864</v>
       </c>
       <c r="B865" t="n">
-        <v>0.41359375</v>
+        <v>0.89171875</v>
       </c>
     </row>
     <row r="866">
@@ -7357,7 +7357,7 @@
         <v>865</v>
       </c>
       <c r="B866" t="n">
-        <v>0.8143750000000001</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="867">
@@ -7365,7 +7365,7 @@
         <v>866</v>
       </c>
       <c r="B867" t="n">
-        <v>0.70609375</v>
+        <v>0.960625</v>
       </c>
     </row>
     <row r="868">
@@ -7373,7 +7373,7 @@
         <v>867</v>
       </c>
       <c r="B868" t="n">
-        <v>0.8903125000000001</v>
+        <v>0.96484375</v>
       </c>
     </row>
     <row r="869">
@@ -7381,7 +7381,7 @@
         <v>868</v>
       </c>
       <c r="B869" t="n">
-        <v>0.926875</v>
+        <v>0.881875</v>
       </c>
     </row>
     <row r="870">
@@ -7389,7 +7389,7 @@
         <v>869</v>
       </c>
       <c r="B870" t="n">
-        <v>0.60203125</v>
+        <v>0.91421875</v>
       </c>
     </row>
     <row r="871">
@@ -7397,7 +7397,7 @@
         <v>870</v>
       </c>
       <c r="B871" t="n">
-        <v>0.80734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="872">
@@ -7405,7 +7405,7 @@
         <v>871</v>
       </c>
       <c r="B872" t="n">
-        <v>0.578125</v>
+        <v>0.9578125</v>
       </c>
     </row>
     <row r="873">
@@ -7413,7 +7413,7 @@
         <v>872</v>
       </c>
       <c r="B873" t="n">
-        <v>0.95921875</v>
+        <v>0.68078125</v>
       </c>
     </row>
     <row r="874">
@@ -7421,7 +7421,7 @@
         <v>873</v>
       </c>
       <c r="B874" t="n">
-        <v>0.73421875</v>
+        <v>0.9325</v>
       </c>
     </row>
     <row r="875">
@@ -7429,7 +7429,7 @@
         <v>874</v>
       </c>
       <c r="B875" t="n">
-        <v>0.89734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="876">
@@ -7437,7 +7437,7 @@
         <v>875</v>
       </c>
       <c r="B876" t="n">
-        <v>0.859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="877">
@@ -7445,7 +7445,7 @@
         <v>876</v>
       </c>
       <c r="B877" t="n">
-        <v>0.8003125</v>
+        <v>0.97890625</v>
       </c>
     </row>
     <row r="878">
@@ -7453,7 +7453,7 @@
         <v>877</v>
       </c>
       <c r="B878" t="n">
-        <v>0.82421875</v>
+        <v>0.9254687500000001</v>
       </c>
     </row>
     <row r="879">
@@ -7461,7 +7461,7 @@
         <v>878</v>
       </c>
       <c r="B879" t="n">
-        <v>0.5696874999999999</v>
+        <v>0.94375</v>
       </c>
     </row>
     <row r="880">
@@ -7469,7 +7469,7 @@
         <v>879</v>
       </c>
       <c r="B880" t="n">
-        <v>0.870625</v>
+        <v>0.97046875</v>
       </c>
     </row>
     <row r="881">
@@ -7477,7 +7477,7 @@
         <v>880</v>
       </c>
       <c r="B881" t="n">
-        <v>0.8509375</v>
+        <v>0.76515625</v>
       </c>
     </row>
     <row r="882">
@@ -7485,7 +7485,7 @@
         <v>881</v>
       </c>
       <c r="B882" t="n">
-        <v>0.6934374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="883">
@@ -7493,7 +7493,7 @@
         <v>882</v>
       </c>
       <c r="B883" t="n">
-        <v>0.8284374999999999</v>
+        <v>0.97328125</v>
       </c>
     </row>
     <row r="884">
@@ -7501,7 +7501,7 @@
         <v>883</v>
       </c>
       <c r="B884" t="n">
-        <v>0</v>
+        <v>0.9521875</v>
       </c>
     </row>
     <row r="885">
@@ -7509,7 +7509,7 @@
         <v>884</v>
       </c>
       <c r="B885" t="n">
-        <v>0.938125</v>
+        <v>0.9325</v>
       </c>
     </row>
     <row r="886">
@@ -7517,7 +7517,7 @@
         <v>885</v>
       </c>
       <c r="B886" t="n">
-        <v>0</v>
+        <v>0.97890625</v>
       </c>
     </row>
     <row r="887">
@@ -7525,7 +7525,7 @@
         <v>886</v>
       </c>
       <c r="B887" t="n">
-        <v>0.960625</v>
+        <v>0.97890625</v>
       </c>
     </row>
     <row r="888">
@@ -7533,7 +7533,7 @@
         <v>887</v>
       </c>
       <c r="B888" t="n">
-        <v>0</v>
+        <v>0.86640625</v>
       </c>
     </row>
     <row r="889">
@@ -7541,7 +7541,7 @@
         <v>888</v>
       </c>
       <c r="B889" t="n">
-        <v>0.8171875</v>
+        <v>0.7384375</v>
       </c>
     </row>
     <row r="890">
@@ -7549,7 +7549,7 @@
         <v>889</v>
       </c>
       <c r="B890" t="n">
-        <v>0.8509375</v>
+        <v>0.9746875</v>
       </c>
     </row>
     <row r="891">
@@ -7557,7 +7557,7 @@
         <v>890</v>
       </c>
       <c r="B891" t="n">
-        <v>0</v>
+        <v>0.960625</v>
       </c>
     </row>
     <row r="892">
@@ -7565,7 +7565,7 @@
         <v>891</v>
       </c>
       <c r="B892" t="n">
-        <v>0.9746875</v>
+        <v>0.9071875</v>
       </c>
     </row>
     <row r="893">
@@ -7573,7 +7573,7 @@
         <v>892</v>
       </c>
       <c r="B893" t="n">
-        <v>0.7454687499999999</v>
+        <v>0.971875</v>
       </c>
     </row>
     <row r="894">
@@ -7581,7 +7581,7 @@
         <v>893</v>
       </c>
       <c r="B894" t="n">
-        <v>0.8495312500000001</v>
+        <v>0.97046875</v>
       </c>
     </row>
     <row r="895">
@@ -7589,7 +7589,7 @@
         <v>894</v>
       </c>
       <c r="B895" t="n">
-        <v>0</v>
+        <v>0.98171875</v>
       </c>
     </row>
     <row r="896">
@@ -7597,7 +7597,7 @@
         <v>895</v>
       </c>
       <c r="B896" t="n">
-        <v>0.9662500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="897">
@@ -7605,7 +7605,7 @@
         <v>896</v>
       </c>
       <c r="B897" t="n">
-        <v>0.75109375</v>
+        <v>0.77640625</v>
       </c>
     </row>
     <row r="898">
@@ -7613,7 +7613,7 @@
         <v>897</v>
       </c>
       <c r="B898" t="n">
-        <v>0.8003125</v>
+        <v>0.7145312500000001</v>
       </c>
     </row>
     <row r="899">
@@ -7621,7 +7621,7 @@
         <v>898</v>
       </c>
       <c r="B899" t="n">
-        <v>0</v>
+        <v>0.5978125</v>
       </c>
     </row>
     <row r="900">
@@ -7629,7 +7629,7 @@
         <v>899</v>
       </c>
       <c r="B900" t="n">
-        <v>0.7215625</v>
+        <v>0.74265625</v>
       </c>
     </row>
     <row r="901">
@@ -7637,7 +7637,7 @@
         <v>900</v>
       </c>
       <c r="B901" t="n">
-        <v>0.9775</v>
+        <v>0.9690625</v>
       </c>
     </row>
     <row r="902">
@@ -7645,7 +7645,7 @@
         <v>901</v>
       </c>
       <c r="B902" t="n">
-        <v>0</v>
+        <v>0.9803125</v>
       </c>
     </row>
     <row r="903">
@@ -7661,7 +7661,7 @@
         <v>903</v>
       </c>
       <c r="B904" t="n">
-        <v>0.82703125</v>
+        <v>0.77359375</v>
       </c>
     </row>
     <row r="905">
@@ -7677,7 +7677,7 @@
         <v>905</v>
       </c>
       <c r="B906" t="n">
-        <v>0.62453125</v>
+        <v>0.971875</v>
       </c>
     </row>
     <row r="907">
@@ -7693,7 +7693,7 @@
         <v>907</v>
       </c>
       <c r="B908" t="n">
-        <v>0.88046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="909">
@@ -7701,7 +7701,7 @@
         <v>908</v>
       </c>
       <c r="B909" t="n">
-        <v>0.6399999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="910">
@@ -7709,7 +7709,7 @@
         <v>909</v>
       </c>
       <c r="B910" t="n">
-        <v>0.8171875</v>
+        <v>0.91703125</v>
       </c>
     </row>
     <row r="911">
@@ -7717,7 +7717,7 @@
         <v>910</v>
       </c>
       <c r="B911" t="n">
-        <v>0.6146875000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="912">
@@ -7725,7 +7725,7 @@
         <v>911</v>
       </c>
       <c r="B912" t="n">
-        <v>0.77640625</v>
+        <v>0.9803125</v>
       </c>
     </row>
     <row r="913">
@@ -7733,7 +7733,7 @@
         <v>912</v>
       </c>
       <c r="B913" t="n">
-        <v>0.55</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="914">
@@ -7749,7 +7749,7 @@
         <v>914</v>
       </c>
       <c r="B915" t="n">
-        <v>0.78484375</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="916">
@@ -7757,7 +7757,7 @@
         <v>915</v>
       </c>
       <c r="B916" t="n">
-        <v>0</v>
+        <v>0.9662500000000001</v>
       </c>
     </row>
     <row r="917">
@@ -7765,7 +7765,7 @@
         <v>916</v>
       </c>
       <c r="B917" t="n">
-        <v>0.5584375</v>
+        <v>0.983125</v>
       </c>
     </row>
     <row r="918">
@@ -7773,7 +7773,7 @@
         <v>917</v>
       </c>
       <c r="B918" t="n">
-        <v>0.8987499999999999</v>
+        <v>0.97609375</v>
       </c>
     </row>
     <row r="919">
@@ -7781,7 +7781,7 @@
         <v>918</v>
       </c>
       <c r="B919" t="n">
-        <v>0</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="920">
@@ -7789,7 +7789,7 @@
         <v>919</v>
       </c>
       <c r="B920" t="n">
-        <v>0.4332812500000001</v>
+        <v>0.971875</v>
       </c>
     </row>
     <row r="921">
@@ -7797,7 +7797,7 @@
         <v>920</v>
       </c>
       <c r="B921" t="n">
-        <v>0</v>
+        <v>0.769375</v>
       </c>
     </row>
     <row r="922">
@@ -7805,7 +7805,7 @@
         <v>921</v>
       </c>
       <c r="B922" t="n">
-        <v>0.555625</v>
+        <v>0.90578125</v>
       </c>
     </row>
     <row r="923">
@@ -7813,7 +7813,7 @@
         <v>922</v>
       </c>
       <c r="B923" t="n">
-        <v>0.7989062499999999</v>
+        <v>0.81578125</v>
       </c>
     </row>
     <row r="924">
@@ -7821,7 +7821,7 @@
         <v>923</v>
       </c>
       <c r="B924" t="n">
-        <v>0.5246875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="925">
@@ -7829,7 +7829,7 @@
         <v>924</v>
       </c>
       <c r="B925" t="n">
-        <v>0</v>
+        <v>0.9803125</v>
       </c>
     </row>
     <row r="926">
@@ -7837,7 +7837,7 @@
         <v>925</v>
       </c>
       <c r="B926" t="n">
-        <v>0.48953125</v>
+        <v>0.9282812499999999</v>
       </c>
     </row>
     <row r="927">
@@ -7845,7 +7845,7 @@
         <v>926</v>
       </c>
       <c r="B927" t="n">
-        <v>0</v>
+        <v>0.96765625</v>
       </c>
     </row>
     <row r="928">
@@ -7853,7 +7853,7 @@
         <v>927</v>
       </c>
       <c r="B928" t="n">
-        <v>0</v>
+        <v>0.983125</v>
       </c>
     </row>
     <row r="929">
@@ -7861,7 +7861,7 @@
         <v>928</v>
       </c>
       <c r="B929" t="n">
-        <v>0</v>
+        <v>0.7778125</v>
       </c>
     </row>
     <row r="930">
@@ -7869,7 +7869,7 @@
         <v>929</v>
       </c>
       <c r="B930" t="n">
-        <v>0.971875</v>
+        <v>0.91984375</v>
       </c>
     </row>
     <row r="931">
@@ -7877,7 +7877,7 @@
         <v>930</v>
       </c>
       <c r="B931" t="n">
-        <v>0</v>
+        <v>0.56546875</v>
       </c>
     </row>
     <row r="932">
@@ -7885,7 +7885,7 @@
         <v>931</v>
       </c>
       <c r="B932" t="n">
-        <v>0</v>
+        <v>0.82140625</v>
       </c>
     </row>
     <row r="933">
@@ -7893,7 +7893,7 @@
         <v>932</v>
       </c>
       <c r="B933" t="n">
-        <v>0</v>
+        <v>0.971875</v>
       </c>
     </row>
     <row r="934">
@@ -7901,7 +7901,7 @@
         <v>933</v>
       </c>
       <c r="B934" t="n">
-        <v>0</v>
+        <v>0.46703125</v>
       </c>
     </row>
     <row r="935">
@@ -7909,7 +7909,7 @@
         <v>934</v>
       </c>
       <c r="B935" t="n">
-        <v>0</v>
+        <v>0.8565625</v>
       </c>
     </row>
     <row r="936">
@@ -7917,7 +7917,7 @@
         <v>935</v>
       </c>
       <c r="B936" t="n">
-        <v>0</v>
+        <v>0.97046875</v>
       </c>
     </row>
     <row r="937">
@@ -7925,7 +7925,7 @@
         <v>936</v>
       </c>
       <c r="B937" t="n">
-        <v>0</v>
+        <v>0.9634374999999999</v>
       </c>
     </row>
     <row r="938">
@@ -7933,7 +7933,7 @@
         <v>937</v>
       </c>
       <c r="B938" t="n">
-        <v>0</v>
+        <v>0.87765625</v>
       </c>
     </row>
     <row r="939">
@@ -7949,7 +7949,7 @@
         <v>939</v>
       </c>
       <c r="B940" t="n">
-        <v>0.5795312500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="941">
@@ -7957,7 +7957,7 @@
         <v>940</v>
       </c>
       <c r="B941" t="n">
-        <v>0</v>
+        <v>0.904375</v>
       </c>
     </row>
     <row r="942">
@@ -7965,7 +7965,7 @@
         <v>941</v>
       </c>
       <c r="B942" t="n">
-        <v>0</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="943">
@@ -7981,7 +7981,7 @@
         <v>943</v>
       </c>
       <c r="B944" t="n">
-        <v>0</v>
+        <v>0.63578125</v>
       </c>
     </row>
     <row r="945">
@@ -8005,7 +8005,7 @@
         <v>946</v>
       </c>
       <c r="B947" t="n">
-        <v>0</v>
+        <v>0.97890625</v>
       </c>
     </row>
     <row r="948">
@@ -8045,7 +8045,7 @@
         <v>951</v>
       </c>
       <c r="B952" t="n">
-        <v>0</v>
+        <v>0.9746875</v>
       </c>
     </row>
     <row r="953">
@@ -8053,7 +8053,7 @@
         <v>952</v>
       </c>
       <c r="B953" t="n">
-        <v>0</v>
+        <v>0.9803125</v>
       </c>
     </row>
     <row r="954">
@@ -8061,7 +8061,7 @@
         <v>953</v>
       </c>
       <c r="B954" t="n">
-        <v>0.8903125000000001</v>
+        <v>0.7145312500000001</v>
       </c>
     </row>
     <row r="955">
@@ -8069,7 +8069,7 @@
         <v>954</v>
       </c>
       <c r="B955" t="n">
-        <v>0.7384375</v>
+        <v>0.64140625</v>
       </c>
     </row>
     <row r="956">
@@ -8077,7 +8077,7 @@
         <v>955</v>
       </c>
       <c r="B956" t="n">
-        <v>0</v>
+        <v>0.96765625</v>
       </c>
     </row>
     <row r="957">
@@ -8085,7 +8085,7 @@
         <v>956</v>
       </c>
       <c r="B957" t="n">
-        <v>0</v>
+        <v>0.803125</v>
       </c>
     </row>
     <row r="958">
@@ -8109,7 +8109,7 @@
         <v>959</v>
       </c>
       <c r="B960" t="n">
-        <v>0</v>
+        <v>0.78625</v>
       </c>
     </row>
     <row r="961">
@@ -8117,7 +8117,7 @@
         <v>960</v>
       </c>
       <c r="B961" t="n">
-        <v>0</v>
+        <v>0.8790625</v>
       </c>
     </row>
     <row r="962">
@@ -8133,7 +8133,7 @@
         <v>962</v>
       </c>
       <c r="B963" t="n">
-        <v>0</v>
+        <v>0.9803125</v>
       </c>
     </row>
     <row r="964">
@@ -8157,7 +8157,7 @@
         <v>965</v>
       </c>
       <c r="B966" t="n">
-        <v>0</v>
+        <v>0.960625</v>
       </c>
     </row>
     <row r="967">
@@ -8165,7 +8165,7 @@
         <v>966</v>
       </c>
       <c r="B967" t="n">
-        <v>0</v>
+        <v>0.9254687500000001</v>
       </c>
     </row>
     <row r="968">
@@ -8173,7 +8173,7 @@
         <v>967</v>
       </c>
       <c r="B968" t="n">
-        <v>0</v>
+        <v>0.91703125</v>
       </c>
     </row>
     <row r="969">
@@ -8181,7 +8181,7 @@
         <v>968</v>
       </c>
       <c r="B969" t="n">
-        <v>0</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="970">
@@ -8189,7 +8189,7 @@
         <v>969</v>
       </c>
       <c r="B970" t="n">
-        <v>0</v>
+        <v>0.9690625</v>
       </c>
     </row>
     <row r="971">
@@ -8197,7 +8197,7 @@
         <v>970</v>
       </c>
       <c r="B971" t="n">
-        <v>0</v>
+        <v>0.89171875</v>
       </c>
     </row>
     <row r="972">
@@ -8205,7 +8205,7 @@
         <v>971</v>
       </c>
       <c r="B972" t="n">
-        <v>0</v>
+        <v>0.713125</v>
       </c>
     </row>
     <row r="973">
@@ -8229,7 +8229,7 @@
         <v>974</v>
       </c>
       <c r="B975" t="n">
-        <v>0</v>
+        <v>0.9803125</v>
       </c>
     </row>
     <row r="976">
@@ -8245,7 +8245,7 @@
         <v>976</v>
       </c>
       <c r="B977" t="n">
-        <v>0.713125</v>
+        <v>0.949375</v>
       </c>
     </row>
     <row r="978">
@@ -8253,7 +8253,7 @@
         <v>977</v>
       </c>
       <c r="B978" t="n">
-        <v>0.3925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="979">
@@ -8269,7 +8269,7 @@
         <v>979</v>
       </c>
       <c r="B980" t="n">
-        <v>0</v>
+        <v>0.8846875</v>
       </c>
     </row>
     <row r="981">
@@ -8277,7 +8277,7 @@
         <v>980</v>
       </c>
       <c r="B981" t="n">
-        <v>0</v>
+        <v>0.95359375</v>
       </c>
     </row>
     <row r="982">
@@ -8325,7 +8325,7 @@
         <v>986</v>
       </c>
       <c r="B987" t="n">
-        <v>0</v>
+        <v>0.39671875</v>
       </c>
     </row>
     <row r="988">
@@ -8333,7 +8333,7 @@
         <v>987</v>
       </c>
       <c r="B988" t="n">
-        <v>0</v>
+        <v>0.6231249999999999</v>
       </c>
     </row>
     <row r="989">
@@ -8349,7 +8349,7 @@
         <v>989</v>
       </c>
       <c r="B990" t="n">
-        <v>0</v>
+        <v>0.9310937500000001</v>
       </c>
     </row>
     <row r="991">
@@ -8357,7 +8357,7 @@
         <v>990</v>
       </c>
       <c r="B991" t="n">
-        <v>0.49796875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="992">
@@ -8365,7 +8365,7 @@
         <v>991</v>
       </c>
       <c r="B992" t="n">
-        <v>0</v>
+        <v>0.9353125</v>
       </c>
     </row>
     <row r="993">
@@ -8373,7 +8373,7 @@
         <v>992</v>
       </c>
       <c r="B993" t="n">
-        <v>0.48671875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="994">
@@ -8381,7 +8381,7 @@
         <v>993</v>
       </c>
       <c r="B994" t="n">
-        <v>0.4206249999999999</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="995">
@@ -8389,7 +8389,7 @@
         <v>994</v>
       </c>
       <c r="B995" t="n">
-        <v>0</v>
+        <v>0.8987499999999999</v>
       </c>
     </row>
     <row r="996">
@@ -8405,7 +8405,7 @@
         <v>996</v>
       </c>
       <c r="B997" t="n">
-        <v>0</v>
+        <v>0.47265625</v>
       </c>
     </row>
     <row r="998">
@@ -8421,7 +8421,7 @@
         <v>998</v>
       </c>
       <c r="B999" t="n">
-        <v>0</v>
+        <v>0.96484375</v>
       </c>
     </row>
     <row r="1000">
@@ -8429,7 +8429,7 @@
         <v>999</v>
       </c>
       <c r="B1000" t="n">
-        <v>0</v>
+        <v>0.89453125</v>
       </c>
     </row>
     <row r="1001">
